--- a/rcads/data/xls/21_ItemStems.xlsx
+++ b/rcads/data/xls/21_ItemStems.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_21_ItemStems"/>
   </sheets>
   <definedNames>
-    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3182</definedName>
+    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3370</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3182"/>
+  <dimension ref="A1:E3370"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -44115,7 +44115,7 @@
         <v>2</v>
       </c>
       <c r="D2295" s="0">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E2295" s="0" t="inlineStr">
         <is>
@@ -58523,2545 +58523,6117 @@
     </row>
     <row outlineLevel="0" r="3049">
       <c r="A3049" s="0">
-        <v>3132</v>
+        <v>3313</v>
       </c>
       <c r="B3049" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3049" s="0">
         <v>1</v>
       </c>
       <c r="D3049" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3049" s="0" t="inlineStr">
         <is>
-          <t>Бринем се када мислим да је неко љут на мене</t>
+          <t>Mi preoccupo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3050">
       <c r="A3050" s="0">
-        <v>3133</v>
+        <v>3314</v>
       </c>
       <c r="B3050" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3050" s="0">
         <v>1</v>
       </c>
       <c r="D3050" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3050" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да будем далеко од својих родитеља</t>
+          <t>Mi sento triste o vuoto/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3051">
       <c r="A3051" s="0">
-        <v>3134</v>
+        <v>3315</v>
       </c>
       <c r="B3051" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3051" s="0">
         <v>1</v>
       </c>
       <c r="D3051" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3051" s="0" t="inlineStr">
         <is>
-          <t>Узнемиравају ме лоше или чудне мисли и слике у мојој глави</t>
+          <t>Quando ho un problema, provo una strana sensazione allo stomaco</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3052">
       <c r="A3052" s="0">
-        <v>3135</v>
+        <v>3316</v>
       </c>
       <c r="B3052" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3052" s="0">
         <v>1</v>
       </c>
       <c r="D3052" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3052" s="0" t="inlineStr">
         <is>
-          <t>Имам проблема са спавањем</t>
+          <t>Mi preoccupo quando penso di aver fatto male qualcosa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3053">
       <c r="A3053" s="0">
-        <v>3136</v>
+        <v>3317</v>
       </c>
       <c r="B3053" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3053" s="0">
         <v>1</v>
       </c>
       <c r="D3053" s="0">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E3053" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ћу урадити лоше задатке на часу</t>
+          <t>Ho paura di stare da solo/a a casa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3054">
       <c r="A3054" s="0">
-        <v>3137</v>
+        <v>3318</v>
       </c>
       <c r="B3054" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3054" s="0">
         <v>1</v>
       </c>
       <c r="D3054" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E3054" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ће се десити нешто лоше некоме у мојој породици</t>
+          <t>Niente è più divertente per me</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3055">
       <c r="A3055" s="0">
-        <v>3138</v>
+        <v>3319</v>
       </c>
       <c r="B3055" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3055" s="0">
         <v>1</v>
       </c>
       <c r="D3055" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3055" s="0" t="inlineStr">
         <is>
-          <t>Одједном осећам као да не могу да дишем без икаквог разлога</t>
+          <t>Ho paura quando devo fare una prova</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3056">
       <c r="A3056" s="0">
-        <v>3139</v>
+        <v>3320</v>
       </c>
       <c r="B3056" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3056" s="0">
         <v>1</v>
       </c>
       <c r="D3056" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3056" s="0" t="inlineStr">
         <is>
-          <t>Имам пробелема са апетитом</t>
+          <t>Mi preoccupo quando penso che qualcuno sia arrabbiato con me</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3057">
       <c r="A3057" s="0">
-        <v>3140</v>
+        <v>3321</v>
       </c>
       <c r="B3057" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3057" s="0">
         <v>1</v>
       </c>
       <c r="D3057" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3057" s="0" t="inlineStr">
         <is>
-          <t>Морам стално да проверавам да ли сам све урадио/ла како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+          <t>Mi preoccupa l'idea di essere lontano/a dai miei genitori</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3058">
       <c r="A3058" s="0">
-        <v>3141</v>
+        <v>3322</v>
       </c>
       <c r="B3058" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3058" s="0">
         <v>1</v>
       </c>
       <c r="D3058" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3058" s="0" t="inlineStr">
         <is>
-          <t>Плашим се ако морам да спавам сам/а</t>
+          <t>Sono infastidito/a da pensieri cattivi o sciocchi o immagini nella mia mente</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3059">
       <c r="A3059" s="0">
-        <v>3142</v>
+        <v>3323</v>
       </c>
       <c r="B3059" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3059" s="0">
         <v>1</v>
       </c>
       <c r="D3059" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E3059" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да идем у школу јер се осећам нервозно или уплашено</t>
+          <t>Ho problemi a dormire</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3060">
       <c r="A3060" s="0">
-        <v>3143</v>
+        <v>3324</v>
       </c>
       <c r="B3060" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3060" s="0">
         <v>1</v>
       </c>
       <c r="D3060" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3060" s="0" t="inlineStr">
         <is>
-          <t>Немам енергије да радим ствари</t>
+          <t>Sono preoccupato/a che quel che devo fare a scuola andrà male</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3061">
       <c r="A3061" s="0">
-        <v>3144</v>
+        <v>3325</v>
       </c>
       <c r="B3061" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3061" s="0">
         <v>1</v>
       </c>
       <c r="D3061" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3061" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да бих могао/ла да испаднем смешан/а другима</t>
+          <t>Sono preoccupato/a che qualcosa di terribile accadrà a qualcuno della mia famiglia</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3062">
       <c r="A3062" s="0">
-        <v>3145</v>
+        <v>3326</v>
       </c>
       <c r="B3062" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3062" s="0">
         <v>1</v>
       </c>
       <c r="D3062" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3062" s="0" t="inlineStr">
         <is>
-          <t>Много сам уморан/а</t>
+          <t>Mi sento improvvisamente come se non riuscissi a respirare, anche quando non ce n'è nessun motivo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3063">
       <c r="A3063" s="0">
-        <v>3146</v>
+        <v>3327</v>
       </c>
       <c r="B3063" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3063" s="0">
         <v>1</v>
       </c>
       <c r="D3063" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3063" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ће ми се дешавати лоше ствари</t>
+          <t>Ho problemi di appetito</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3064">
       <c r="A3064" s="0">
-        <v>3147</v>
+        <v>3328</v>
       </c>
       <c r="B3064" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3064" s="0">
         <v>1</v>
       </c>
       <c r="D3064" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3064" s="0" t="inlineStr">
         <is>
-          <t>Не могу да се ослободим лоших или чудних мисли из главе</t>
+          <t>Devo continuare a controllare di aver fatto le cose nel modo giusto (ad esempio, che l’interruttore sia spento o la porta sia chiusa)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3065">
       <c r="A3065" s="0">
-        <v>3148</v>
+        <v>3329</v>
       </c>
       <c r="B3065" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3065" s="0">
         <v>1</v>
       </c>
       <c r="D3065" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3065" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, срце ми брзо куца</t>
+          <t>Ho paura di dormire da solo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3066">
       <c r="A3066" s="0">
-        <v>3149</v>
+        <v>3330</v>
       </c>
       <c r="B3066" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3066" s="0">
         <v>1</v>
       </c>
       <c r="D3066" s="0">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3066" s="0" t="inlineStr">
         <is>
-          <t>Не могу да мислим јасно</t>
+          <t>Ho problemi ad andare a scuola la mattina perché mi sento nervoso/a o spaventato/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3067">
       <c r="A3067" s="0">
-        <v>3150</v>
+        <v>3331</v>
       </c>
       <c r="B3067" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3067" s="0">
         <v>1</v>
       </c>
       <c r="D3067" s="0">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E3067" s="0" t="inlineStr">
         <is>
-          <t>Одједном почнем да дрхтим или се тресем без икаквог разлога</t>
+          <t>Non ho energia per fare le cose</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3068">
       <c r="A3068" s="0">
-        <v>3151</v>
+        <v>3332</v>
       </c>
       <c r="B3068" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3068" s="0">
         <v>1</v>
       </c>
       <c r="D3068" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3068" s="0" t="inlineStr">
         <is>
-          <t>Бринем да ће ми се десити нешто лоше</t>
+          <t>Mi preoccupo di poter sembrare sciocco/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3069">
       <c r="A3069" s="0">
-        <v>3152</v>
+        <v>3333</v>
       </c>
       <c r="B3069" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3069" s="0">
         <v>1</v>
       </c>
       <c r="D3069" s="0">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3069" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, осећам да дрхтим</t>
+          <t>Sono molto stanco/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3070">
       <c r="A3070" s="0">
-        <v>3153</v>
+        <v>3334</v>
       </c>
       <c r="B3070" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3070" s="0">
         <v>1</v>
       </c>
       <c r="D3070" s="0">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E3070" s="0" t="inlineStr">
         <is>
-          <t>Осећам се безвредно</t>
+          <t>Sono preoccupato/a che mi capiteranno delle cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3071">
       <c r="A3071" s="0">
-        <v>3154</v>
+        <v>3335</v>
       </c>
       <c r="B3071" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3071" s="0">
         <v>1</v>
       </c>
       <c r="D3071" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3071" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да не правим грешке</t>
+          <t>Sembra che io non riesca a togliermi dalla testa pensieri brutti o sciocchi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3072">
       <c r="A3072" s="0">
-        <v>3155</v>
+        <v>3336</v>
       </c>
       <c r="B3072" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3072" s="0">
         <v>1</v>
       </c>
       <c r="D3072" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3072" s="0" t="inlineStr">
         <is>
-          <t>Морам да мислим о одређеним мислима (као бројеви или речи) да бих спечио/ла да се деси нешто лоше</t>
+          <t>Quando ho un problema, il mio cuore batte molto velocemente</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3073">
       <c r="A3073" s="0">
-        <v>3156</v>
+        <v>3337</v>
       </c>
       <c r="B3073" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3073" s="0">
         <v>1</v>
       </c>
       <c r="D3073" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E3073" s="0" t="inlineStr">
         <is>
-          <t>Бринем се шта други људи мисле о мени</t>
+          <t>Non riesco a pensare in modo lucido</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3074">
       <c r="A3074" s="0">
-        <v>3157</v>
+        <v>3338</v>
       </c>
       <c r="B3074" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3074" s="0">
         <v>1</v>
       </c>
       <c r="D3074" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3074" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да будем на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+          <t>Improvvisamente inizio a tremare o ad agitarmi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3075">
       <c r="A3075" s="0">
-        <v>3158</v>
+        <v>3339</v>
       </c>
       <c r="B3075" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3075" s="0">
         <v>1</v>
       </c>
       <c r="D3075" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3075" s="0" t="inlineStr">
         <is>
-          <t>Одједном се осећам јако уплашено без икаквог разлога</t>
+          <t>Mi preoccupo che mi possa accadere qualcosa di brutto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3076">
       <c r="A3076" s="0">
-        <v>3159</v>
+        <v>3340</v>
       </c>
       <c r="B3076" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3076" s="0">
         <v>1</v>
       </c>
       <c r="D3076" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3076" s="0" t="inlineStr">
         <is>
-          <t>Бринем се шта ће се десити</t>
+          <t>Quando ho un problema, mi sento tremare</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3077">
       <c r="A3077" s="0">
-        <v>3160</v>
+        <v>3341</v>
       </c>
       <c r="B3077" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3077" s="0">
         <v>1</v>
       </c>
       <c r="D3077" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3077" s="0" t="inlineStr">
         <is>
-          <t>Одједном ми се заврти у глави без икаквог разлога</t>
+          <t>Mi sento inutile</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3078">
       <c r="A3078" s="0">
-        <v>3161</v>
+        <v>3342</v>
       </c>
       <c r="B3078" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3078" s="0">
         <v>1</v>
       </c>
       <c r="D3078" s="0">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3078" s="0" t="inlineStr">
         <is>
-          <t>Размишљам о смрти</t>
+          <t>Fare errori mi preoccupa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3079">
       <c r="A3079" s="0">
-        <v>3162</v>
+        <v>3343</v>
       </c>
       <c r="B3079" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3079" s="0">
         <v>1</v>
       </c>
       <c r="D3079" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3079" s="0" t="inlineStr">
         <is>
-          <t>Уплашим се када треба да причам пред целим разредом</t>
+          <t>Devo pensare cose particolari (ad esempio numeri o parole) per impedire che succedano cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3080">
       <c r="A3080" s="0">
-        <v>3163</v>
+        <v>3344</v>
       </c>
       <c r="B3080" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3080" s="0">
         <v>1</v>
       </c>
       <c r="D3080" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3080" s="0" t="inlineStr">
         <is>
-          <t>Моје срце одједном почне пребрзо да куца без икаквог разлога</t>
+          <t>Mi preoccupa quello che gli altri pensano di me</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3081">
       <c r="A3081" s="0">
-        <v>3164</v>
+        <v>3345</v>
       </c>
       <c r="B3081" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3081" s="0">
         <v>1</v>
       </c>
       <c r="D3081" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3081" s="0" t="inlineStr">
         <is>
-          <t>Чини ми се као да не желим да се покрећем</t>
+          <t>Ho paura di stare in posti affollati (come centri commerciali, cinema, autobus, parchi giochi affollati)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3082">
       <c r="A3082" s="0">
-        <v>3165</v>
+        <v>3346</v>
       </c>
       <c r="B3082" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3082" s="0">
         <v>1</v>
       </c>
       <c r="D3082" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E3082" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ћу изненада имати осећај страха, иако нема чега да се плашим</t>
+          <t>All’improvviso mi sento davvero spaventato/a senza alcuna ragione</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3083">
       <c r="A3083" s="0">
-        <v>3166</v>
+        <v>3347</v>
       </c>
       <c r="B3083" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3083" s="0">
         <v>1</v>
       </c>
       <c r="D3083" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3083" s="0" t="inlineStr">
         <is>
-          <t>Морам да радим неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+          <t>Mi preoccupo di quello che sta per succedere</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3084">
       <c r="A3084" s="0">
-        <v>3167</v>
+        <v>3348</v>
       </c>
       <c r="B3084" s="0">
+        <v>36</v>
+      </c>
+      <c r="C3084" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3084" s="0">
         <v>27</v>
       </c>
-      <c r="C3084" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3084" s="0">
-        <v>2</v>
-      </c>
       <c r="E3084" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да ћу испасти будала пред другима</t>
+          <t>Improvvisamente svengo o mi sento intontito/a quando non ce n'è motivo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3085">
       <c r="A3085" s="0">
-        <v>3168</v>
+        <v>3349</v>
       </c>
       <c r="B3085" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3085" s="0">
         <v>1</v>
       </c>
       <c r="D3085" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3085" s="0" t="inlineStr">
         <is>
-          <t>Морам да радим неке ствари на одређени начин да бих спречио/ла да се десе лоше ствари</t>
+          <t>Penso alla morte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3086">
       <c r="A3086" s="0">
-        <v>3169</v>
+        <v>3350</v>
       </c>
       <c r="B3086" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3086" s="0">
         <v>1</v>
       </c>
       <c r="D3086" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3086" s="0" t="inlineStr">
         <is>
-          <t>Бринем се када идем у кревет ноћу</t>
+          <t>Ho paura se devo parlare di fronte alla mia classe</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3087">
       <c r="A3087" s="0">
-        <v>3170</v>
+        <v>3351</v>
       </c>
       <c r="B3087" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3087" s="0">
         <v>1</v>
       </c>
       <c r="D3087" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3087" s="0" t="inlineStr">
         <is>
-          <t>Био/ла бих уплашен/а када бих морао/ла да преспавам ван куће</t>
+          <t>Il mio cuore improvvisamente inizia a battere troppo velocemente senza alcuna ragione</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3088">
       <c r="A3088" s="0">
-        <v>3171</v>
+        <v>3352</v>
       </c>
       <c r="B3088" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3088" s="0">
         <v>1</v>
       </c>
       <c r="D3088" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3088" s="0" t="inlineStr">
         <is>
-          <t>Осећам немир</t>
+          <t>Mi sento come se non volessi muovermi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3089">
       <c r="A3089" s="0">
-        <v>3172</v>
+        <v>3353</v>
       </c>
       <c r="B3089" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3089" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3089" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E3089" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине око разних ствари</t>
+          <t>Mi preoccupo di provare all’improvviso una sensazione di paura quando non c’è nulla di cui essere spaventati</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3090">
       <c r="A3090" s="0">
-        <v>3173</v>
+        <v>3354</v>
       </c>
       <c r="B3090" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3090" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3090" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3090" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се осећа тужно или празно</t>
+          <t>Ci sono alcune cose che devo fare più e più volte (come lavarmi le mani, pulire o mettere le cose in un certo ordine)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3091">
       <c r="A3091" s="0">
-        <v>3174</v>
+        <v>3355</v>
       </c>
       <c r="B3091" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3091" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3091" s="0">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E3091" s="0" t="inlineStr">
         <is>
-          <t>Када моје дете има неки проблем, онда има чудан осећај у стомаку</t>
+          <t>Ho paura di rendermi ridicolo/a davanti agli altri</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3092">
       <c r="A3092" s="0">
-        <v>3175</v>
+        <v>3356</v>
       </c>
       <c r="B3092" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3092" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3092" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E3092" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када мисли да је било лоше у нечему</t>
+          <t>Devo fare alcune cose nella maniera giusta per impedire che succedano cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3093">
       <c r="A3093" s="0">
-        <v>3176</v>
+        <v>3357</v>
       </c>
       <c r="B3093" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3093" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3093" s="0">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E3093" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да остане само код куће</t>
+          <t>Sono preoccupato/a quando vado a letto la sera</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3094">
       <c r="A3094" s="0">
-        <v>3177</v>
+        <v>3358</v>
       </c>
       <c r="B3094" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3094" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3094" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E3094" s="0" t="inlineStr">
         <is>
-          <t>Мом детету ништа више није забавно</t>
+          <t>Avrei paura se dovessi stare fuori di casa la notte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3095">
       <c r="A3095" s="0">
-        <v>3178</v>
+        <v>3359</v>
       </c>
       <c r="B3095" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3095" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3095" s="0">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E3095" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се уплаши када треба да има неки тест</t>
+          <t>Mi sento irrequieto/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3096">
       <c r="A3096" s="0">
-        <v>3179</v>
+        <v>3360</v>
       </c>
       <c r="B3096" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3096" s="0">
         <v>2</v>
       </c>
       <c r="D3096" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3096" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када мисли да је неко љут на њу/њега</t>
+          <t>Si preoccupa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3097">
       <c r="A3097" s="0">
-        <v>3180</v>
+        <v>3361</v>
       </c>
       <c r="B3097" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3097" s="0">
         <v>2</v>
       </c>
       <c r="D3097" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3097" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да буде одвојено од нас</t>
+          <t>Si sente triste o vuoto/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3098">
       <c r="A3098" s="0">
-        <v>3181</v>
+        <v>3362</v>
       </c>
       <c r="B3098" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3098" s="0">
         <v>2</v>
       </c>
       <c r="D3098" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3098" s="0" t="inlineStr">
         <is>
-          <t>Моје дете узнемиравају лоше или чудне мисли и слике у његовој/њеној глави</t>
+          <t>Quando ha un problema, prova una strana sensazione allo stomaco</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3099">
       <c r="A3099" s="0">
-        <v>3182</v>
+        <v>3363</v>
       </c>
       <c r="B3099" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3099" s="0">
         <v>2</v>
       </c>
       <c r="D3099" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3099" s="0" t="inlineStr">
         <is>
-          <t>Моје дете има проблема са спавањем</t>
+          <t>Si preoccupa quando pensa di aver fatto male qualcosa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3100">
       <c r="A3100" s="0">
-        <v>3183</v>
+        <v>3364</v>
       </c>
       <c r="B3100" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3100" s="0">
         <v>2</v>
       </c>
       <c r="D3100" s="0">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E3100" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће урадити лоше задатке на часу</t>
+          <t>Ha paura di stare da solo a casa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3101">
       <c r="A3101" s="0">
-        <v>3184</v>
+        <v>3365</v>
       </c>
       <c r="B3101" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3101" s="0">
         <v>2</v>
       </c>
       <c r="D3101" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E3101" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће се десити нешто лоше некоме у нашој породици</t>
+          <t>Niente più lo/la diverte tanto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3102">
       <c r="A3102" s="0">
-        <v>3185</v>
+        <v>3366</v>
       </c>
       <c r="B3102" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3102" s="0">
         <v>2</v>
       </c>
       <c r="D3102" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3102" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се одједном осећа као да не може да дише без неког разлога</t>
+          <t>Ha paura quando deve fare una prova</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3103">
       <c r="A3103" s="0">
-        <v>3186</v>
+        <v>3367</v>
       </c>
       <c r="B3103" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3103" s="0">
         <v>2</v>
       </c>
       <c r="D3103" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3103" s="0" t="inlineStr">
         <is>
-          <t>Моје дете има пробелема са апетитом</t>
+          <t>Si preoccupa quando pensa che qualcuno sia arrabbiato con lui/lei</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3104">
       <c r="A3104" s="0">
-        <v>3187</v>
+        <v>3368</v>
       </c>
       <c r="B3104" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3104" s="0">
         <v>2</v>
       </c>
       <c r="D3104" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3104" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора стално да проверава да ли је све урадило како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+          <t>Lo/la preoccupa l'idea di essere lontano/a da lei (genitore o caregiver)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3105">
       <c r="A3105" s="0">
-        <v>3188</v>
+        <v>3369</v>
       </c>
       <c r="B3105" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3105" s="0">
         <v>2</v>
       </c>
       <c r="D3105" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3105" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да спава само</t>
+          <t>È infastidito da pensieri cattivi o sciocchi o immagini nella sua mente</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3106">
       <c r="A3106" s="0">
-        <v>3189</v>
+        <v>3370</v>
       </c>
       <c r="B3106" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3106" s="0">
         <v>2</v>
       </c>
       <c r="D3106" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E3106" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да иде у школу јер се осећа нервозно или уплашено</t>
+          <t>Ha problemi a dormire</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3107">
       <c r="A3107" s="0">
-        <v>3190</v>
+        <v>3371</v>
       </c>
       <c r="B3107" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3107" s="0">
         <v>2</v>
       </c>
       <c r="D3107" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3107" s="0" t="inlineStr">
         <is>
-          <t>Моје дете нема енергије да ради ствари</t>
+          <t>È preoccupato/a di andare male a scuola</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3108">
       <c r="A3108" s="0">
-        <v>3191</v>
+        <v>3372</v>
       </c>
       <c r="B3108" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3108" s="0">
         <v>2</v>
       </c>
       <c r="D3108" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3108" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да би могало да испадне смешано другима</t>
+          <t>Si preoccupa che qualcosa di terribile accadrà a qualcuno della famiglia</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3109">
       <c r="A3109" s="0">
-        <v>3192</v>
+        <v>3373</v>
       </c>
       <c r="B3109" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3109" s="0">
         <v>2</v>
       </c>
       <c r="D3109" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3109" s="0" t="inlineStr">
         <is>
-          <t>Моје дете је много уморно</t>
+          <t>Si sente improvvisamente come se non riuscisse a respirare, anche quando non ce n'è nessun motivo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3110">
       <c r="A3110" s="0">
-        <v>3193</v>
+        <v>3374</v>
       </c>
       <c r="B3110" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3110" s="0">
         <v>2</v>
       </c>
       <c r="D3110" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3110" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће му/јој се дешавати лоше ствари</t>
+          <t>Ha problemi di appetito</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3111">
       <c r="A3111" s="0">
-        <v>3194</v>
+        <v>3375</v>
       </c>
       <c r="B3111" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3111" s="0">
         <v>2</v>
       </c>
       <c r="D3111" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3111" s="0" t="inlineStr">
         <is>
-          <t>Моје дете не може да се ослободи лоших или чудних мисли из своје главе</t>
+          <t>Deve continuare a controllare di aver fatto le cose nel modo giusto (ad esempio, che l’interruttore sia spento o la porta sia chiusa)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3112">
       <c r="A3112" s="0">
-        <v>3195</v>
+        <v>3376</v>
       </c>
       <c r="B3112" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3112" s="0">
         <v>2</v>
       </c>
       <c r="D3112" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3112" s="0" t="inlineStr">
         <is>
-          <t>Када моје дете има неки проблем, срце му/јој брзо куца</t>
+          <t>Ha paura di dormire da solo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3113">
       <c r="A3113" s="0">
-        <v>3196</v>
+        <v>3377</v>
       </c>
       <c r="B3113" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3113" s="0">
         <v>2</v>
       </c>
       <c r="D3113" s="0">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3113" s="0" t="inlineStr">
         <is>
-          <t>Моје дете не може да мисли јасно</t>
+          <t>Ha problemi ad andare a scuola la mattina perché si sente nervoso o spaventato</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3114">
       <c r="A3114" s="0">
-        <v>3197</v>
+        <v>3378</v>
       </c>
       <c r="B3114" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3114" s="0">
         <v>2</v>
       </c>
       <c r="D3114" s="0">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E3114" s="0" t="inlineStr">
         <is>
-          <t>Моје дете одједном почне да дрхти или се тресе и без неког разлога</t>
+          <t>Non ha energia per fare le cose</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3115">
       <c r="A3115" s="0">
-        <v>3198</v>
+        <v>3379</v>
       </c>
       <c r="B3115" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3115" s="0">
         <v>2</v>
       </c>
       <c r="D3115" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3115" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине да ће му/јој се десити нешто лоше</t>
+          <t>Si preoccupa di poter sembrare sciocco/a</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3116">
       <c r="A3116" s="0">
-        <v>3199</v>
+        <v>3380</v>
       </c>
       <c r="B3116" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3116" s="0">
         <v>2</v>
       </c>
       <c r="D3116" s="0">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3116" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, моје дете осећа да дрхти</t>
+          <t>È molto stanco</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3117">
       <c r="A3117" s="0">
-        <v>3200</v>
+        <v>3381</v>
       </c>
       <c r="B3117" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3117" s="0">
         <v>2</v>
       </c>
       <c r="D3117" s="0">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E3117" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се осећа безвредно</t>
+          <t>Si preoccupa che gli/le accadano cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3118">
       <c r="A3118" s="0">
-        <v>3201</v>
+        <v>3382</v>
       </c>
       <c r="B3118" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3118" s="0">
         <v>2</v>
       </c>
       <c r="D3118" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3118" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине да ће правити грешке</t>
+          <t>Sembra non riuscire a togliersi dalla testa pensieri brutti o sciocchi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3119">
       <c r="A3119" s="0">
-        <v>3202</v>
+        <v>3383</v>
       </c>
       <c r="B3119" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3119" s="0">
         <v>2</v>
       </c>
       <c r="D3119" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3119" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да мисли о одређеним мислима (као бројеви или речи) да би спечио да се деси нешто лоше</t>
+          <t>Quando ha un problema, il suo cuore batte molto velocemente</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3120">
       <c r="A3120" s="0">
-        <v>3203</v>
+        <v>3384</v>
       </c>
       <c r="B3120" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3120" s="0">
         <v>2</v>
       </c>
       <c r="D3120" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E3120" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине шта други људи мисле о њему/њој</t>
+          <t>Non riesce a pensare in modo lucido</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3121">
       <c r="A3121" s="0">
-        <v>3204</v>
+        <v>3385</v>
       </c>
       <c r="B3121" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3121" s="0">
         <v>2</v>
       </c>
       <c r="D3121" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3121" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да буде на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+          <t>Inizia improvvisamente a tremare o agitarsi quando non c’è n’ è alcun motivo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3122">
       <c r="A3122" s="0">
-        <v>3205</v>
+        <v>3386</v>
       </c>
       <c r="B3122" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3122" s="0">
         <v>2</v>
       </c>
       <c r="D3122" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3122" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се одједном осећам јако уплашено без икаквог разлога</t>
+          <t>Si preoccupa che gli/le capiti qualcosa di brutto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3123">
       <c r="A3123" s="0">
-        <v>3206</v>
+        <v>3387</v>
       </c>
       <c r="B3123" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3123" s="0">
         <v>2</v>
       </c>
       <c r="D3123" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3123" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине шта ће се десити</t>
+          <t>Quando il mio bambino/ragazzo ha un problema, si sente tremare</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3124">
       <c r="A3124" s="0">
-        <v>3207</v>
+        <v>3388</v>
       </c>
       <c r="B3124" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3124" s="0">
         <v>2</v>
       </c>
       <c r="D3124" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3124" s="0" t="inlineStr">
         <is>
-          <t>Мом детету се одједном заврти у глави када за то нема разлога</t>
+          <t>Si sente inutile</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3125">
       <c r="A3125" s="0">
-        <v>3208</v>
+        <v>3389</v>
       </c>
       <c r="B3125" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3125" s="0">
         <v>2</v>
       </c>
       <c r="D3125" s="0">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3125" s="0" t="inlineStr">
         <is>
-          <t>Моје дете размишља о смрти</t>
+          <t>Fare errori lo/la preoccupa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3126">
       <c r="A3126" s="0">
-        <v>3209</v>
+        <v>3390</v>
       </c>
       <c r="B3126" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3126" s="0">
         <v>2</v>
       </c>
       <c r="D3126" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3126" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се уплаши када треба да прича пред целим разредом</t>
+          <t>Deve pensare a cose particolari (ad esempio numeri o parole) per impedire che succedano cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3127">
       <c r="A3127" s="0">
-        <v>3210</v>
+        <v>3391</v>
       </c>
       <c r="B3127" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3127" s="0">
         <v>2</v>
       </c>
       <c r="D3127" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3127" s="0" t="inlineStr">
         <is>
-          <t>Мом детету изненада почне срце пребрзо да куца без икаквог разлога</t>
+          <t>Si preoccupa di quello che gli altri pensano di lui/lei</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3128">
       <c r="A3128" s="0">
-        <v>3211</v>
+        <v>3392</v>
       </c>
       <c r="B3128" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3128" s="0">
         <v>2</v>
       </c>
       <c r="D3128" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3128" s="0" t="inlineStr">
         <is>
-          <t>Моје дете изгледа као да не жели да се покреће</t>
+          <t>Ha paura di stare in posti affollati (come centri commerciali, cinema, autobus, parchi giochi affollati)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3129">
       <c r="A3129" s="0">
-        <v>3212</v>
+        <v>3393</v>
       </c>
       <c r="B3129" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3129" s="0">
         <v>2</v>
       </c>
       <c r="D3129" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E3129" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће изненада имати осећај страха, иако нема чега да се плашим</t>
+          <t>All’improvviso si sentirà davvero spaventato senza alcuna ragione</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3130">
       <c r="A3130" s="0">
-        <v>3213</v>
+        <v>3394</v>
       </c>
       <c r="B3130" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3130" s="0">
         <v>2</v>
       </c>
       <c r="D3130" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3130" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да ради неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+          <t>Si preoccupa di quello che sta per succedere</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3131">
       <c r="A3131" s="0">
-        <v>3214</v>
+        <v>3395</v>
       </c>
       <c r="B3131" s="0">
+        <v>36</v>
+      </c>
+      <c r="C3131" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3131" s="0">
         <v>27</v>
       </c>
-      <c r="C3131" s="0">
-        <v>2</v>
-      </c>
-      <c r="D3131" s="0">
-        <v>2</v>
-      </c>
       <c r="E3131" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да ће испасти будала пред другима</t>
+          <t>Improvvisamente sviene o si sente intontito/a quando non ce n'è motivo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3132">
       <c r="A3132" s="0">
-        <v>3215</v>
+        <v>3396</v>
       </c>
       <c r="B3132" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3132" s="0">
         <v>2</v>
       </c>
       <c r="D3132" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3132" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да ради неке ствари на одређени начин да би спречио/ла да се десе лоше ствари</t>
+          <t>Pensa alla morte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3133">
       <c r="A3133" s="0">
-        <v>3216</v>
+        <v>3397</v>
       </c>
       <c r="B3133" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3133" s="0">
         <v>2</v>
       </c>
       <c r="D3133" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3133" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када иде у кревет ноћу</t>
+          <t>Ha paura se deve parlare di fronte alla classe</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3134">
       <c r="A3134" s="0">
-        <v>3217</v>
+        <v>3398</v>
       </c>
       <c r="B3134" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3134" s="0">
         <v>2</v>
       </c>
       <c r="D3134" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3134" s="0" t="inlineStr">
         <is>
-          <t>Моје дете би било уплашено када би морало да преспава ван куће</t>
+          <t>Il cuore del mio bambino/ragazzo improvvisamente inizia a battere troppo velocemente senza alcuna ragione</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3135">
       <c r="A3135" s="0">
-        <v>3218</v>
+        <v>3399</v>
       </c>
       <c r="B3135" s="0">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3135" s="0">
         <v>2</v>
       </c>
       <c r="D3135" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3135" s="0" t="inlineStr">
         <is>
-          <t>Моје дете осећа немир</t>
+          <t>Si sente come se non volesse muoversi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3136">
       <c r="A3136" s="0">
-        <v>3219</v>
+        <v>3400</v>
       </c>
       <c r="B3136" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3136" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3136" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E3136" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về mọi thứ</t>
+          <t>Si preoccupa di provare all’improvviso una sensazione di paura quando non c’è nulla di cui essere spaventati</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3137">
       <c r="A3137" s="0">
-        <v>3220</v>
+        <v>3401</v>
       </c>
       <c r="B3137" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3137" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3137" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3137" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy buồn bã hoặc trống rỗng</t>
+          <t>Ci sono alcune cose che deve fare più e più volte (come lavarsi le mani, pulire o mettere le cose in un certo ordine)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3138">
       <c r="A3138" s="0">
-        <v>3221</v>
+        <v>3402</v>
       </c>
       <c r="B3138" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3138" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3138" s="0">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E3138" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp một vấn đề, em có cảm giác khó chịu trong dạ dày của mình</t>
+          <t>Ha paura di rendersi ridicolo/a davanti agli altri</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3139">
       <c r="A3139" s="0">
-        <v>3222</v>
+        <v>3403</v>
       </c>
       <c r="B3139" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3139" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3139" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E3139" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng khi nghĩ rằng mình đã làm điều gì đó không tốt</t>
+          <t>Deve fare alcune cose nella maniera giusta per impedire che succedano cose brutte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3140">
       <c r="A3140" s="0">
-        <v>3223</v>
+        <v>3404</v>
       </c>
       <c r="B3140" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3140" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3140" s="0">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E3140" s="0" t="inlineStr">
         <is>
-          <t>Em sẽ cảm thấy sợ khi phải ở nhà một mình</t>
+          <t>È preoccupato/a quando va a letto la sera</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3141">
       <c r="A3141" s="0">
-        <v>3224</v>
+        <v>3405</v>
       </c>
       <c r="B3141" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3141" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3141" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E3141" s="0" t="inlineStr">
         <is>
-          <t>Không còn điều gì vui vẻ nữa</t>
+          <t>Avrebbe paura se dovesse stare fuori di casa la notte</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3142">
       <c r="A3142" s="0">
-        <v>3225</v>
+        <v>3406</v>
       </c>
       <c r="B3142" s="0">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3142" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3142" s="0">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E3142" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi khi phải làm bài kiểm tra</t>
+          <t>Si sente irrequieto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3143">
       <c r="A3143" s="0">
-        <v>3226</v>
+        <v>3407</v>
       </c>
       <c r="B3143" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3143" s="0">
         <v>1</v>
       </c>
       <c r="D3143" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3143" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy lo lắng khi nghĩ rằng có ai đó đang tức giận với em</t>
+          <t>Ngizikhathaza ngezinto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3144">
       <c r="A3144" s="0">
-        <v>3227</v>
+        <v>3408</v>
       </c>
       <c r="B3144" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3144" s="0">
         <v>1</v>
       </c>
       <c r="D3144" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3144" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc phải xa bố mẹ của mình</t>
+          <t>Ngizizwa ngidabukile noma ngingenalutho</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3145">
       <c r="A3145" s="0">
-        <v>3228</v>
+        <v>3409</v>
       </c>
       <c r="B3145" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3145" s="0">
         <v>1</v>
       </c>
       <c r="D3145" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3145" s="0" t="inlineStr">
         <is>
-          <t>Em bị làm phiền bởi những suy nghĩ hoặc hình ảnh xấu hoặc ngớ ngẩn trong tâm trí của em</t>
+          <t>Uma nginenkinga, ngiba nomuzwa engingawuqondi kahle esiswini sami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3146">
       <c r="A3146" s="0">
-        <v>3229</v>
+        <v>3410</v>
       </c>
       <c r="B3146" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3146" s="0">
         <v>1</v>
       </c>
       <c r="D3146" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3146" s="0" t="inlineStr">
         <is>
-          <t>Em bị khó ngủ</t>
+          <t>Ngiyakhathazeka uma ngicabanga ukuthi kukhona okungalungile engikwenzile</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3147">
       <c r="A3147" s="0">
-        <v>3230</v>
+        <v>3411</v>
       </c>
       <c r="B3147" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3147" s="0">
         <v>1</v>
       </c>
       <c r="D3147" s="0">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E3147" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng rằng em sẽ làm bài tập ở trường rất kém</t>
+          <t>Ngangizizwa ngisaba ukuba ngedwa ekhaya</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3148">
       <c r="A3148" s="0">
-        <v>3231</v>
+        <v>3412</v>
       </c>
       <c r="B3148" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3148" s="0">
         <v>1</v>
       </c>
       <c r="D3148" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E3148" s="0" t="inlineStr">
         <is>
-          <t>Em lo rằng điều gì đó khủng khiếp sẽ xảy ra với người thân trong gia đình</t>
+          <t>Akusekho okungijabulisa kakhulu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3149">
       <c r="A3149" s="0">
-        <v>3232</v>
+        <v>3413</v>
       </c>
       <c r="B3149" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3149" s="0">
         <v>1</v>
       </c>
       <c r="D3149" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3149" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên cảm thấy như thể em bị khó thở mà không rõ lý do</t>
+          <t>Ngizizwa ngisaba uma kufanele ngiyohlola</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3150">
       <c r="A3150" s="0">
-        <v>3233</v>
+        <v>3414</v>
       </c>
       <c r="B3150" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3150" s="0">
         <v>1</v>
       </c>
       <c r="D3150" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3150" s="0" t="inlineStr">
         <is>
-          <t>Em có vấn đề với cảm giác thèm ăn của mình</t>
+          <t>Ngizizwa ngikhathazekile uma ngicabanga ukuthi kukhona ongithukuthelele</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3151">
       <c r="A3151" s="0">
-        <v>3234</v>
+        <v>3415</v>
       </c>
       <c r="B3151" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3151" s="0">
         <v>1</v>
       </c>
       <c r="D3151" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3151" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải kiểm tra xem em đã làm đúng chưa (như tắt công tắc chưa hoặc đã khóa cửa chưa)</t>
+          <t>Ngikhathazekile ngokuba kude nomzali wami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3152">
       <c r="A3152" s="0">
-        <v>3235</v>
+        <v>3416</v>
       </c>
       <c r="B3152" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3152" s="0">
         <v>1</v>
       </c>
       <c r="D3152" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3152" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi nếu phải ngủ một mình</t>
+          <t>Ngikhathazwa imicabango emibi noma engasile noma izithombe ngaphakathi engqondweni yami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3153">
       <c r="A3153" s="0">
-        <v>3236</v>
+        <v>3417</v>
       </c>
       <c r="B3153" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3153" s="0">
         <v>1</v>
       </c>
       <c r="D3153" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E3153" s="0" t="inlineStr">
         <is>
-          <t>Em gặp khó khăn khi đến trường vào buổi sáng vì em cảm thấy lo lắng hoặc sợ hãi</t>
+          <t>Nginenkinga yokulala</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3154">
       <c r="A3154" s="0">
-        <v>3237</v>
+        <v>3418</v>
       </c>
       <c r="B3154" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3154" s="0">
         <v>1</v>
       </c>
       <c r="D3154" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3154" s="0" t="inlineStr">
         <is>
-          <t>Em không còn năng lượng cho mọi việc</t>
+          <t>Ngikhathazekile ngokuthi ngizokwenza kabi emsebenzini wami wesikole</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3155">
       <c r="A3155" s="0">
-        <v>3238</v>
+        <v>3419</v>
       </c>
       <c r="B3155" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3155" s="0">
         <v>1</v>
       </c>
       <c r="D3155" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3155" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng mình có thể trông thật ngớ ngẩn</t>
+          <t>Ngikhathazwa ukuthi kukhona into embi ezokwenzeka kumuntu osemndenini wami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3156">
       <c r="A3156" s="0">
-        <v>3239</v>
+        <v>3420</v>
       </c>
       <c r="B3156" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3156" s="0">
         <v>1</v>
       </c>
       <c r="D3156" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3156" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy rất mệt mỏi</t>
+          <t>Ngivele ngizwe sengathi angikwazi ukuphefumula ngokungenasizathu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3157">
       <c r="A3157" s="0">
-        <v>3240</v>
+        <v>3421</v>
       </c>
       <c r="B3157" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3157" s="0">
         <v>1</v>
       </c>
       <c r="D3157" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3157" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng vì những điều tồi tệ có thể xảy ra với em</t>
+          <t>Nginenkinga nesifiso sokudla</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3158">
       <c r="A3158" s="0">
-        <v>3241</v>
+        <v>3422</v>
       </c>
       <c r="B3158" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3158" s="0">
         <v>1</v>
       </c>
       <c r="D3158" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3158" s="0" t="inlineStr">
         <is>
-          <t>Em dường như không thể loại bỏ những suy nghĩ xấu hay ngớ ngẩn ra khỏi đầu</t>
+          <t>Kufanele ngihlale ngibheka ukuthi ngenze izinto ngendlela efanele (njengokuthi iswishi ivaliwe, noma umnyango ukhiyiwe)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3159">
       <c r="A3159" s="0">
-        <v>3242</v>
+        <v>3423</v>
       </c>
       <c r="B3159" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3159" s="0">
         <v>1</v>
       </c>
       <c r="D3159" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3159" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp vấn đề, tim em đập rất nhanh</t>
+          <t>Ngizizwa ngisaba uma kufanele ngilale ngedwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3160">
       <c r="A3160" s="0">
-        <v>3243</v>
+        <v>3424</v>
       </c>
       <c r="B3160" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3160" s="0">
         <v>1</v>
       </c>
       <c r="D3160" s="0">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3160" s="0" t="inlineStr">
         <is>
-          <t>Em không thể suy nghĩ rõ ràng thông suốt</t>
+          <t>Nginenkinga yokuya esikoleni ekuseni ngoba ngizizwa nginovalo noma ngesaba</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3161">
       <c r="A3161" s="0">
-        <v>3244</v>
+        <v>3425</v>
       </c>
       <c r="B3161" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3161" s="0">
         <v>1</v>
       </c>
       <c r="D3161" s="0">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E3161" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên run rẩy hoặc run lên mà không rõ lý do</t>
+          <t>Anginawo amandla okwenza izinto</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3162">
       <c r="A3162" s="0">
-        <v>3245</v>
+        <v>3426</v>
       </c>
       <c r="B3162" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3162" s="0">
         <v>1</v>
       </c>
       <c r="D3162" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3162" s="0" t="inlineStr">
         <is>
-          <t>Em lo rằng chuyện gì đó tồi tệ sẽ xảy ra với mình</t>
+          <t>Ngikhathazekile ngokuthi ngingase ngibukeke ngiyisiwula</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3163">
       <c r="A3163" s="0">
-        <v>3246</v>
+        <v>3427</v>
       </c>
       <c r="B3163" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3163" s="0">
         <v>1</v>
       </c>
       <c r="D3163" s="0">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3163" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp vấn đề, em cảm thấy run rẩy</t>
+          <t>Ngikhathele kakhulu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3164">
       <c r="A3164" s="0">
-        <v>3247</v>
+        <v>3428</v>
       </c>
       <c r="B3164" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3164" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3164" s="0">
         <v>39</v>
       </c>
-      <c r="C3164" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3164" s="0">
-        <v>15</v>
-      </c>
       <c r="E3164" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy mình vô dụng</t>
+          <t>Ngikhathazekile ngokuthi izinto ezimbi zizokwenzeka kimi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3165">
       <c r="A3165" s="0">
-        <v>3248</v>
+        <v>3429</v>
       </c>
       <c r="B3165" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3165" s="0">
         <v>1</v>
       </c>
       <c r="D3165" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3165" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc mình sẽ mắc sai lầm</t>
+          <t>Angiboni ngikhipha imicabango emibi noma engasile ekhanda lami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3166">
       <c r="A3166" s="0">
-        <v>3249</v>
+        <v>3430</v>
       </c>
       <c r="B3166" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3166" s="0">
         <v>1</v>
       </c>
       <c r="D3166" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3166" s="0" t="inlineStr">
         <is>
-          <t>Em phải nghĩ đến những điều đặc biệt (như con số hoặc từ ngữ nào đó) để ngăn những điều tồi tệ xảy ra</t>
+          <t>Uma nginenkinga, inhliziyo yami ishaya kakhulu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3167">
       <c r="A3167" s="0">
-        <v>3250</v>
+        <v>3431</v>
       </c>
       <c r="B3167" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3167" s="0">
         <v>1</v>
       </c>
       <c r="D3167" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E3167" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc người khác nghĩ gì về mình</t>
+          <t>Angikwazi ukucabanga kahle</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3168">
       <c r="A3168" s="0">
-        <v>3251</v>
+        <v>3432</v>
       </c>
       <c r="B3168" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3168" s="0">
         <v>1</v>
       </c>
       <c r="D3168" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3168" s="0" t="inlineStr">
         <is>
-          <t>Em sợ hãi khi ở nơi đông người (như trung tâm thương mại, rạp chiếu phim, xe buýt, sân chơi đông đúc)</t>
+          <t>Ngivele ngithuthumele noma ngiqhaqhazele lapho kungekho isizathu salokhu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3169">
       <c r="A3169" s="0">
-        <v>3252</v>
+        <v>3433</v>
       </c>
       <c r="B3169" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3169" s="0">
         <v>1</v>
       </c>
       <c r="D3169" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3169" s="0" t="inlineStr">
         <is>
-          <t>Đột nhiên em cảm thấy thực sự sợ hãi mà không rõ lý do</t>
+          <t>Ngikhathazekile ngokuthi kukhona okubi okuzokwenzeka kimi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3170">
       <c r="A3170" s="0">
-        <v>3253</v>
+        <v>3434</v>
       </c>
       <c r="B3170" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3170" s="0">
         <v>1</v>
       </c>
       <c r="D3170" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3170" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về những gì sẽ xảy ra</t>
+          <t>Uma nginenkinga, ngizizwa ngiqhaqhazela</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3171">
       <c r="A3171" s="0">
-        <v>3254</v>
+        <v>3435</v>
       </c>
       <c r="B3171" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3171" s="0">
         <v>1</v>
       </c>
       <c r="D3171" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3171" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên cảm thấy chóng mặt hoặc muốn ngất xỉu mà không rõ lý do</t>
+          <t>Ngizizwa ngingento yalutho</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3172">
       <c r="A3172" s="0">
-        <v>3255</v>
+        <v>3436</v>
       </c>
       <c r="B3172" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3172" s="0">
         <v>1</v>
       </c>
       <c r="D3172" s="0">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3172" s="0" t="inlineStr">
         <is>
-          <t>Em nghĩ về cái chết</t>
+          <t>Ngiyakhathazeka ngokwenza amaphutha</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3173">
       <c r="A3173" s="0">
-        <v>3256</v>
+        <v>3437</v>
       </c>
       <c r="B3173" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3173" s="0">
         <v>1</v>
       </c>
       <c r="D3173" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3173" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ nếu em phải nói trước lớp</t>
+          <t>Kufanele ngicabange ngemicabango ekhethekile (njengezinombolo noma amazwi) ukuvimba izinto ezimbi ukuthi zenzeke</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3174">
       <c r="A3174" s="0">
-        <v>3257</v>
+        <v>3438</v>
       </c>
       <c r="B3174" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3174" s="0">
         <v>1</v>
       </c>
       <c r="D3174" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3174" s="0" t="inlineStr">
         <is>
-          <t>Tim em đột nhiên đập quá nhanh mà không rõ lý do</t>
+          <t>Ngiyakhathazeka ngokuthi abanye abantu bacabangani ngami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3175">
       <c r="A3175" s="0">
-        <v>3258</v>
+        <v>3439</v>
       </c>
       <c r="B3175" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3175" s="0">
         <v>1</v>
       </c>
       <c r="D3175" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3175" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy như thể em không muốn cử động</t>
+          <t>Ngesaba ukuba sendaweni egcwele abantu (njengasezinxanxatheleni zezitolo, emibukisweni, amabhasi, izinkundla zokudlala ezimatasa)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3176">
       <c r="A3176" s="0">
-        <v>3259</v>
+        <v>3440</v>
       </c>
       <c r="B3176" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3176" s="0">
         <v>1</v>
       </c>
       <c r="D3176" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E3176" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng rằng mình sẽ đột nhiên cảm thấy sợ hãi dù không có gì đáng sợ cả</t>
+          <t>Ngokuphazima kweso ngizizwa ngisaba ngempela ngaphandle kwesizathu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3177">
       <c r="A3177" s="0">
-        <v>3260</v>
+        <v>3441</v>
       </c>
       <c r="B3177" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3177" s="0">
         <v>1</v>
       </c>
       <c r="D3177" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3177" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải làm một số việc lặp đi lặp lại (như rửa tay, dọn dẹp hoặc sắp xếp mọi thứ theo thứ tự nhất định)</t>
+          <t>Ngikhathazekile ngokuzokwenzeka</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3178">
       <c r="A3178" s="0">
-        <v>3261</v>
+        <v>3442</v>
       </c>
       <c r="B3178" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3178" s="0">
         <v>1</v>
       </c>
       <c r="D3178" s="0">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E3178" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy lo sợ rằng mình sẽ làm điều ngu ngốc trước mặt người khác</t>
+          <t>Ngivele ngibe nesiyezi noma ngiquleke lapho kungekho isizathu salokhu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3179">
       <c r="A3179" s="0">
-        <v>3262</v>
+        <v>3443</v>
       </c>
       <c r="B3179" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3179" s="0">
         <v>1</v>
       </c>
       <c r="D3179" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3179" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải làm một số việc theo đúng cách để tránh những chuyện tồi tệ xảy ra</t>
+          <t>Ngicabanga ngokufa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3180">
       <c r="A3180" s="0">
-        <v>3263</v>
+        <v>3444</v>
       </c>
       <c r="B3180" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3180" s="0">
         <v>1</v>
       </c>
       <c r="D3180" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3180" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng khi đi ngủ vào ban đêm</t>
+          <t>Ngizizwa ngisaba uma kufanele ngikhulume phambi kwekilasi lami</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3181">
       <c r="A3181" s="0">
-        <v>3264</v>
+        <v>3445</v>
       </c>
       <c r="B3181" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3181" s="0">
         <v>1</v>
       </c>
       <c r="D3181" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3181" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi nếu em phải xa nhà qua đêm</t>
+          <t>Inhliziyo yami ivele ishaye ngokushesha ngaphandle kwesizathu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3182">
       <c r="A3182" s="0">
+        <v>3446</v>
+      </c>
+      <c r="B3182" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3182" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3182" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3182" s="0" t="inlineStr">
+        <is>
+          <t>Ngizwa sengathi angifuni ukunyakaza</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3183">
+      <c r="A3183" s="0">
+        <v>3447</v>
+      </c>
+      <c r="B3183" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3183" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3183" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3183" s="0" t="inlineStr">
+        <is>
+          <t>Ngikhathazeka ngokuthi ngizothola ngokuzumayo umuzwa wokwesaba lapho kungenasidingo sokwesaba</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3184">
+      <c r="A3184" s="0">
+        <v>3448</v>
+      </c>
+      <c r="B3184" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3184" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3184" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3184" s="0" t="inlineStr">
+        <is>
+          <t>Kufanele ngenze ezinye izinto ngokuphindaphindiwe (njengokugeza  izandla zami, ukuhlanza noma ukubeka izinto ngokulandelana okuthile)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3185">
+      <c r="A3185" s="0">
+        <v>3449</v>
+      </c>
+      <c r="B3185" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3185" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3185" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3185" s="0" t="inlineStr">
+        <is>
+          <t>Ngizizwa ngisaba ukuthi ngizozenza isilima phambi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3186">
+      <c r="A3186" s="0">
+        <v>3450</v>
+      </c>
+      <c r="B3186" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3186" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3186" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3186" s="0" t="inlineStr">
+        <is>
+          <t>Kufanele ngenze ezinye izinto ngendlela efanele ukuze ngivimbele</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3187">
+      <c r="A3187" s="0">
+        <v>3451</v>
+      </c>
+      <c r="B3187" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3187" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3187" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3187" s="0" t="inlineStr">
+        <is>
+          <t>Ngiyakhathazeka uma ngilala ebusuku</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3188">
+      <c r="A3188" s="0">
+        <v>3452</v>
+      </c>
+      <c r="B3188" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3188" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3188" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3188" s="0" t="inlineStr">
+        <is>
+          <t>Ngingazizwa nginovalo uma kufanele ngiqhele ekhaya ebusuku</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3189">
+      <c r="A3189" s="0">
+        <v>3453</v>
+      </c>
+      <c r="B3189" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3189" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3189" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3189" s="0" t="inlineStr">
+        <is>
+          <t>Ngizizwa ngingahlaliseki</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3190">
+      <c r="A3190" s="0">
+        <v>3454</v>
+      </c>
+      <c r="B3190" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3190" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3190" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3190" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazeka ngezinto</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3191">
+      <c r="A3191" s="0">
+        <v>3455</v>
+      </c>
+      <c r="B3191" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3191" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3191" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3191" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa idabukile noma ingenalutho</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3192">
+      <c r="A3192" s="0">
+        <v>3456</v>
+      </c>
+      <c r="B3192" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3192" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3192" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3192" s="0" t="inlineStr">
+        <is>
+          <t>Uma ingane yami inenkinga, ithola okuhlekisayo ezwa esiswini sakhe</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3193">
+      <c r="A3193" s="0">
+        <v>3457</v>
+      </c>
+      <c r="B3193" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3193" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3193" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3193" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami iyakhathazeka uma icabanga ukuthi ikwenzile kabi kokuthile</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3194">
+      <c r="A3194" s="0">
+        <v>3458</v>
+      </c>
+      <c r="B3194" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3194" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3194" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3194" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa isaba ukuba yedwa ekhaya</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3195">
+      <c r="A3195" s="0">
+        <v>3459</v>
+      </c>
+      <c r="B3195" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3195" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3195" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3195" s="0" t="inlineStr">
+        <is>
+          <t>Ayisekho into emnandi enganeni yami</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3196">
+      <c r="A3196" s="0">
+        <v>3460</v>
+      </c>
+      <c r="B3196" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3196" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3196" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3196" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa yethukile lapho ihlola</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3197">
+      <c r="A3197" s="0">
+        <v>3461</v>
+      </c>
+      <c r="B3197" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3197" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3197" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3197" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami iyakhathazeka uma icabanga ukuthi kukhona umuntu amthukuthelele</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3198">
+      <c r="A3198" s="0">
+        <v>3462</v>
+      </c>
+      <c r="B3198" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3198" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3198" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3198" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuba kude nami</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3199">
+      <c r="A3199" s="0">
+        <v>3463</v>
+      </c>
+      <c r="B3199" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3199" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3199" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3199" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ihlushwa imicabango emibi noma engasile noma izithombe engqondweni yakhe</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3200">
+      <c r="A3200" s="0">
+        <v>3464</v>
+      </c>
+      <c r="B3200" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3200" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3200" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3200" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami inenkinga yokulala</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3201">
+      <c r="A3201" s="0">
+        <v>3465</v>
+      </c>
+      <c r="B3201" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3201" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3201" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3201" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokwenza kabi emsebenzini wesikole</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3202">
+      <c r="A3202" s="0">
+        <v>3466</v>
+      </c>
+      <c r="B3202" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3202" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3202" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3202" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuthi kukhona okubi okuzokwenzeka othile emndenini</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3203">
+      <c r="A3203" s="0">
+        <v>3467</v>
+      </c>
+      <c r="B3203" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3203" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3203" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3203" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ivele ibe sengathi ayikwazi ukuphefumula lapho singekho isizathu salokhu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3204">
+      <c r="A3204" s="0">
+        <v>3468</v>
+      </c>
+      <c r="B3204" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3204" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3204" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3204" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami inezinkinga ngesifiso sayo sokudla</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3205">
+      <c r="A3205" s="0">
+        <v>3469</v>
+      </c>
+      <c r="B3205" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3205" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3205" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3205" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami kufanele ihlale ibheka ukuthi isikwenzile izinto zilungile (njengokungathi iswishi ivaliwe, noma umnyango ukhiyiwe)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3206">
+      <c r="A3206" s="0">
+        <v>3470</v>
+      </c>
+      <c r="B3206" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3206" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3206" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3206" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa isaba ukulala yodwa</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3207">
+      <c r="A3207" s="0">
+        <v>3471</v>
+      </c>
+      <c r="B3207" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3207" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3207" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3207" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami inenkinga yokuya esikoleni ekuseni ngenxa yokuzwa uvalo noma ukwesaba</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3208">
+      <c r="A3208" s="0">
+        <v>3472</v>
+      </c>
+      <c r="B3208" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3208" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3208" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3208" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ayinawo amandla ezinto</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3209">
+      <c r="A3209" s="0">
+        <v>3473</v>
+      </c>
+      <c r="B3209" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3209" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3209" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3209" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokubukeka isilima</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3210">
+      <c r="A3210" s="0">
+        <v>3474</v>
+      </c>
+      <c r="B3210" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3210" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3210" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3210" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathele kakhulu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3211">
+      <c r="A3211" s="0">
+        <v>3475</v>
+      </c>
+      <c r="B3211" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3211" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3211" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3211" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuthi kuzokwenzeka izinto ezimbi kuye</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3212">
+      <c r="A3212" s="0">
+        <v>3476</v>
+      </c>
+      <c r="B3212" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3212" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3212" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3212" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ayibonakali ikhipha imicabango emibi noma engasile ikhanda lakhe</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3213">
+      <c r="A3213" s="0">
+        <v>3477</v>
+      </c>
+      <c r="B3213" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3213" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3213" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3213" s="0" t="inlineStr">
+        <is>
+          <t>Uma ingane yami inenkinga, inhliziyo yayo ishaya ngokushesha ngempela</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3214">
+      <c r="A3214" s="0">
+        <v>3478</v>
+      </c>
+      <c r="B3214" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3214" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3214" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3214" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ayikwazi ukucabanga kahle</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3215">
+      <c r="A3215" s="0">
+        <v>3479</v>
+      </c>
+      <c r="B3215" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3215" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3215" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3215" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ivele iqale ukuthuthumela noma ukuqhaqhazela lapho asikho isizathu salokhu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3216">
+      <c r="A3216" s="0">
+        <v>3480</v>
+      </c>
+      <c r="B3216" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3216" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3216" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3216" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuthi kukhona okubi okuzokwenzekakuye</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3217">
+      <c r="A3217" s="0">
+        <v>3481</v>
+      </c>
+      <c r="B3217" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3217" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3217" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3217" s="0" t="inlineStr">
+        <is>
+          <t>Uma ingane yami inenkinga, izizwa iqhaqhazela</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3218">
+      <c r="A3218" s="0">
+        <v>3482</v>
+      </c>
+      <c r="B3218" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3218" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3218" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3218" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa ingelutho</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3219">
+      <c r="A3219" s="0">
+        <v>3483</v>
+      </c>
+      <c r="B3219" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3219" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3219" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3219" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazeka ngokwenza amaphutha</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3220">
+      <c r="A3220" s="0">
+        <v>3484</v>
+      </c>
+      <c r="B3220" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3220" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3220" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3220" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami kufanele icabange ngemicabango ekhethekile (njengezinombolo noma amagama) ukuvimba izinto ezimbi ukuthi zenzeke</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3221">
+      <c r="A3221" s="0">
+        <v>3485</v>
+      </c>
+      <c r="B3221" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3221" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3221" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3221" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazeka ngokuthi abanye abantu bacabangani ngayo</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3222">
+      <c r="A3222" s="0">
+        <v>3486</v>
+      </c>
+      <c r="B3222" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3222" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3222" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3222" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami yesaba ukuba sendaweni egcwele abantu (like izindawo zokuthenga, amamuvi, amabhasi, izinkundla zokudlala ezimatasa)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3223">
+      <c r="A3223" s="0">
+        <v>3487</v>
+      </c>
+      <c r="B3223" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3223" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3223" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3223" s="0" t="inlineStr">
+        <is>
+          <t>Kusenjalo ingane yami izozizwa isaba impela cha isizathu nhlobo</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3224">
+      <c r="A3224" s="0">
+        <v>3488</v>
+      </c>
+      <c r="B3224" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3224" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3224" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3224" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuthi kuzokwenzekani</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3225">
+      <c r="A3225" s="0">
+        <v>3489</v>
+      </c>
+      <c r="B3225" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3225" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3225" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3225" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami iba nesiyezi noma iquleke kungazelelwe lapho akusona isizathu salokhu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3226">
+      <c r="A3226" s="0">
+        <v>3490</v>
+      </c>
+      <c r="B3226" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3226" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3226" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3226" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami icabanga ngokufa</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3227">
+      <c r="A3227" s="0">
+        <v>3491</v>
+      </c>
+      <c r="B3227" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3227" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3227" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3227" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami iyesaba uma kufanele ikhulume phambi kwayo ikilasi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3228">
+      <c r="A3228" s="0">
+        <v>3492</v>
+      </c>
+      <c r="B3228" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3228" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3228" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3228" s="0" t="inlineStr">
+        <is>
+          <t>Inhliziyo yengane yami ivele ishaye ngokushesha ngaphandle kwesizathu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3229">
+      <c r="A3229" s="0">
+        <v>3493</v>
+      </c>
+      <c r="B3229" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3229" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3229" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3229" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izwa sengathi ayifuni ukunyakaza</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3230">
+      <c r="A3230" s="0">
+        <v>3494</v>
+      </c>
+      <c r="B3230" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3230" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3230" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3230" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ikhathazekile ngokuthi izothola a umuzwa wokwesaba lapho kungekho lutho okumelwe lwesabe</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3231">
+      <c r="A3231" s="0">
+        <v>3495</v>
+      </c>
+      <c r="B3231" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3231" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3231" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3231" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami kufanele yenze ezinye izinto ngokuphindaphindiwe (njenge ukugeza izandla, ukuhlanza, noma ukuhlela izinto ngendlela ethile)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3232">
+      <c r="A3232" s="0">
+        <v>3496</v>
+      </c>
+      <c r="B3232" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3232" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3232" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3232" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa isaba ukuthi izokwenza isilima yena phambi kwabantu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3233">
+      <c r="A3233" s="0">
+        <v>3497</v>
+      </c>
+      <c r="B3233" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3233" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3233" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3233" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami kufanele yenze ezinye izinto ngendlela efanele ukumisa izinto ezimbi ukuthi zingenzeki</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3234">
+      <c r="A3234" s="0">
+        <v>3498</v>
+      </c>
+      <c r="B3234" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3234" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3234" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3234" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami iyakhathazeka uma ilele ebusuku</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3235">
+      <c r="A3235" s="0">
+        <v>3499</v>
+      </c>
+      <c r="B3235" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3235" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3235" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3235" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami ingazizwa isaba uma kufanele ingahambi kusuka ekhaya ebusuku</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3236">
+      <c r="A3236" s="0">
+        <v>3500</v>
+      </c>
+      <c r="B3236" s="0">
+        <v>41</v>
+      </c>
+      <c r="C3236" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3236" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3236" s="0" t="inlineStr">
+        <is>
+          <t>Ingane yami izizwa ingaphumuli</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3237">
+      <c r="A3237" s="0">
+        <v>3132</v>
+      </c>
+      <c r="B3237" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3237" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3237" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3237" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се када мислим да је неко љут на мене</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3238">
+      <c r="A3238" s="0">
+        <v>3133</v>
+      </c>
+      <c r="B3238" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3238" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3238" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3238" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да будем далеко од својих родитеља</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3239">
+      <c r="A3239" s="0">
+        <v>3134</v>
+      </c>
+      <c r="B3239" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3239" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3239" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3239" s="0" t="inlineStr">
+        <is>
+          <t>Узнемиравају ме лоше или чудне мисли и слике у мојој глави</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3240">
+      <c r="A3240" s="0">
+        <v>3135</v>
+      </c>
+      <c r="B3240" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3240" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3240" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3240" s="0" t="inlineStr">
+        <is>
+          <t>Имам проблема са спавањем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3241">
+      <c r="A3241" s="0">
+        <v>3136</v>
+      </c>
+      <c r="B3241" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3241" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3241" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3241" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ћу урадити лоше задатке на часу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3242">
+      <c r="A3242" s="0">
+        <v>3137</v>
+      </c>
+      <c r="B3242" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3242" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3242" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3242" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ће се десити нешто лоше некоме у мојој породици</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3243">
+      <c r="A3243" s="0">
+        <v>3138</v>
+      </c>
+      <c r="B3243" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3243" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3243" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3243" s="0" t="inlineStr">
+        <is>
+          <t>Одједном осећам као да не могу да дишем без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3244">
+      <c r="A3244" s="0">
+        <v>3139</v>
+      </c>
+      <c r="B3244" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3244" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3244" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3244" s="0" t="inlineStr">
+        <is>
+          <t>Имам пробелема са апетитом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3245">
+      <c r="A3245" s="0">
+        <v>3140</v>
+      </c>
+      <c r="B3245" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3245" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3245" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3245" s="0" t="inlineStr">
+        <is>
+          <t>Морам стално да проверавам да ли сам све урадио/ла како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3246">
+      <c r="A3246" s="0">
+        <v>3141</v>
+      </c>
+      <c r="B3246" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3246" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3246" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3246" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се ако морам да спавам сам/а</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3247">
+      <c r="A3247" s="0">
+        <v>3142</v>
+      </c>
+      <c r="B3247" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3247" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3247" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3247" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да идем у школу јер се осећам нервозно или уплашено</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3248">
+      <c r="A3248" s="0">
+        <v>3143</v>
+      </c>
+      <c r="B3248" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3248" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3248" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3248" s="0" t="inlineStr">
+        <is>
+          <t>Немам енергије да радим ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3249">
+      <c r="A3249" s="0">
+        <v>3144</v>
+      </c>
+      <c r="B3249" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3249" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3249" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3249" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да бих могао/ла да испаднем смешан/а другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3250">
+      <c r="A3250" s="0">
+        <v>3145</v>
+      </c>
+      <c r="B3250" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3250" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3250" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3250" s="0" t="inlineStr">
+        <is>
+          <t>Много сам уморан/а</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3251">
+      <c r="A3251" s="0">
+        <v>3146</v>
+      </c>
+      <c r="B3251" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3251" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3251" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3251" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ће ми се дешавати лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3252">
+      <c r="A3252" s="0">
+        <v>3147</v>
+      </c>
+      <c r="B3252" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3252" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3252" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3252" s="0" t="inlineStr">
+        <is>
+          <t>Не могу да се ослободим лоших или чудних мисли из главе</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3253">
+      <c r="A3253" s="0">
+        <v>3148</v>
+      </c>
+      <c r="B3253" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3253" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3253" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3253" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, срце ми брзо куца</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3254">
+      <c r="A3254" s="0">
+        <v>3149</v>
+      </c>
+      <c r="B3254" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3254" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3254" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3254" s="0" t="inlineStr">
+        <is>
+          <t>Не могу да мислим јасно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3255">
+      <c r="A3255" s="0">
+        <v>3150</v>
+      </c>
+      <c r="B3255" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3255" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3255" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3255" s="0" t="inlineStr">
+        <is>
+          <t>Одједном почнем да дрхтим или се тресем без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3256">
+      <c r="A3256" s="0">
+        <v>3151</v>
+      </c>
+      <c r="B3256" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3256" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3256" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3256" s="0" t="inlineStr">
+        <is>
+          <t>Бринем да ће ми се десити нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3257">
+      <c r="A3257" s="0">
+        <v>3152</v>
+      </c>
+      <c r="B3257" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3257" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3257" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3257" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, осећам да дрхтим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3258">
+      <c r="A3258" s="0">
+        <v>3153</v>
+      </c>
+      <c r="B3258" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3258" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3258" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3258" s="0" t="inlineStr">
+        <is>
+          <t>Осећам се безвредно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3259">
+      <c r="A3259" s="0">
+        <v>3154</v>
+      </c>
+      <c r="B3259" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3259" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3259" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3259" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да не правим грешке</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3260">
+      <c r="A3260" s="0">
+        <v>3155</v>
+      </c>
+      <c r="B3260" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3260" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3260" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3260" s="0" t="inlineStr">
+        <is>
+          <t>Морам да мислим о одређеним мислима (као бројеви или речи) да бих спечио/ла да се деси нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3261">
+      <c r="A3261" s="0">
+        <v>3156</v>
+      </c>
+      <c r="B3261" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3261" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3261" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3261" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се шта други људи мисле о мени</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3262">
+      <c r="A3262" s="0">
+        <v>3157</v>
+      </c>
+      <c r="B3262" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3262" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3262" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3262" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да будем на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3263">
+      <c r="A3263" s="0">
+        <v>3158</v>
+      </c>
+      <c r="B3263" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3263" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3263" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3263" s="0" t="inlineStr">
+        <is>
+          <t>Одједном се осећам јако уплашено без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3264">
+      <c r="A3264" s="0">
+        <v>3159</v>
+      </c>
+      <c r="B3264" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3264" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3264" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3264" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се шта ће се десити</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3265">
+      <c r="A3265" s="0">
+        <v>3160</v>
+      </c>
+      <c r="B3265" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3265" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3265" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3265" s="0" t="inlineStr">
+        <is>
+          <t>Одједном ми се заврти у глави без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3266">
+      <c r="A3266" s="0">
+        <v>3161</v>
+      </c>
+      <c r="B3266" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3266" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3266" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3266" s="0" t="inlineStr">
+        <is>
+          <t>Размишљам о смрти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3267">
+      <c r="A3267" s="0">
+        <v>3162</v>
+      </c>
+      <c r="B3267" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3267" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3267" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3267" s="0" t="inlineStr">
+        <is>
+          <t>Уплашим се када треба да причам пред целим разредом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3268">
+      <c r="A3268" s="0">
+        <v>3163</v>
+      </c>
+      <c r="B3268" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3268" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3268" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3268" s="0" t="inlineStr">
+        <is>
+          <t>Моје срце одједном почне пребрзо да куца без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3269">
+      <c r="A3269" s="0">
+        <v>3164</v>
+      </c>
+      <c r="B3269" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3269" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3269" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3269" s="0" t="inlineStr">
+        <is>
+          <t>Чини ми се као да не желим да се покрећем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3270">
+      <c r="A3270" s="0">
+        <v>3165</v>
+      </c>
+      <c r="B3270" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3270" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3270" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3270" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ћу изненада имати осећај страха, иако нема чега да се плашим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3271">
+      <c r="A3271" s="0">
+        <v>3166</v>
+      </c>
+      <c r="B3271" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3271" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3271" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3271" s="0" t="inlineStr">
+        <is>
+          <t>Морам да радим неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3272">
+      <c r="A3272" s="0">
+        <v>3167</v>
+      </c>
+      <c r="B3272" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3272" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3272" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3272" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да ћу испасти будала пред другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3273">
+      <c r="A3273" s="0">
+        <v>3168</v>
+      </c>
+      <c r="B3273" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3273" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3273" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3273" s="0" t="inlineStr">
+        <is>
+          <t>Морам да радим неке ствари на одређени начин да бих спречио/ла да се десе лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3274">
+      <c r="A3274" s="0">
+        <v>3169</v>
+      </c>
+      <c r="B3274" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3274" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3274" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3274" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се када идем у кревет ноћу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3275">
+      <c r="A3275" s="0">
+        <v>3170</v>
+      </c>
+      <c r="B3275" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3275" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3275" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3275" s="0" t="inlineStr">
+        <is>
+          <t>Био/ла бих уплашен/а када бих морао/ла да преспавам ван куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3276">
+      <c r="A3276" s="0">
+        <v>3171</v>
+      </c>
+      <c r="B3276" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3276" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3276" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3276" s="0" t="inlineStr">
+        <is>
+          <t>Осећам немир</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3277">
+      <c r="A3277" s="0">
+        <v>3172</v>
+      </c>
+      <c r="B3277" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3277" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3277" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3277" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине око разних ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3278">
+      <c r="A3278" s="0">
+        <v>3173</v>
+      </c>
+      <c r="B3278" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3278" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3278" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3278" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се осећа тужно или празно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3279">
+      <c r="A3279" s="0">
+        <v>3174</v>
+      </c>
+      <c r="B3279" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3279" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3279" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3279" s="0" t="inlineStr">
+        <is>
+          <t>Када моје дете има неки проблем, онда има чудан осећај у стомаку</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3280">
+      <c r="A3280" s="0">
+        <v>3175</v>
+      </c>
+      <c r="B3280" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3280" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3280" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3280" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када мисли да је било лоше у нечему</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3281">
+      <c r="A3281" s="0">
+        <v>3176</v>
+      </c>
+      <c r="B3281" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3281" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3281" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3281" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да остане само код куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3282">
+      <c r="A3282" s="0">
+        <v>3177</v>
+      </c>
+      <c r="B3282" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3282" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3282" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3282" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету ништа више није забавно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3283">
+      <c r="A3283" s="0">
+        <v>3178</v>
+      </c>
+      <c r="B3283" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3283" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3283" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3283" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се уплаши када треба да има неки тест</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3284">
+      <c r="A3284" s="0">
+        <v>3179</v>
+      </c>
+      <c r="B3284" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3284" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3284" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3284" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када мисли да је неко љут на њу/њега</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3285">
+      <c r="A3285" s="0">
+        <v>3180</v>
+      </c>
+      <c r="B3285" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3285" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3285" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3285" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да буде одвојено од нас</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3286">
+      <c r="A3286" s="0">
+        <v>3181</v>
+      </c>
+      <c r="B3286" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3286" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3286" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3286" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете узнемиравају лоше или чудне мисли и слике у његовој/њеној глави</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3287">
+      <c r="A3287" s="0">
+        <v>3182</v>
+      </c>
+      <c r="B3287" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3287" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3287" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3287" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете има проблема са спавањем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3288">
+      <c r="A3288" s="0">
+        <v>3183</v>
+      </c>
+      <c r="B3288" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3288" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3288" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3288" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће урадити лоше задатке на часу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3289">
+      <c r="A3289" s="0">
+        <v>3184</v>
+      </c>
+      <c r="B3289" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3289" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3289" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3289" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће се десити нешто лоше некоме у нашој породици</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3290">
+      <c r="A3290" s="0">
+        <v>3185</v>
+      </c>
+      <c r="B3290" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3290" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3290" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3290" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се одједном осећа као да не може да дише без неког разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3291">
+      <c r="A3291" s="0">
+        <v>3186</v>
+      </c>
+      <c r="B3291" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3291" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3291" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3291" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете има пробелема са апетитом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3292">
+      <c r="A3292" s="0">
+        <v>3187</v>
+      </c>
+      <c r="B3292" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3292" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3292" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3292" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора стално да проверава да ли је све урадило како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3293">
+      <c r="A3293" s="0">
+        <v>3188</v>
+      </c>
+      <c r="B3293" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3293" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3293" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3293" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да спава само</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3294">
+      <c r="A3294" s="0">
+        <v>3189</v>
+      </c>
+      <c r="B3294" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3294" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3294" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3294" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да иде у школу јер се осећа нервозно или уплашено</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3295">
+      <c r="A3295" s="0">
+        <v>3190</v>
+      </c>
+      <c r="B3295" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3295" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3295" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3295" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете нема енергије да ради ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3296">
+      <c r="A3296" s="0">
+        <v>3191</v>
+      </c>
+      <c r="B3296" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3296" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3296" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3296" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да би могало да испадне смешано другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3297">
+      <c r="A3297" s="0">
+        <v>3192</v>
+      </c>
+      <c r="B3297" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3297" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3297" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3297" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете је много уморно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3298">
+      <c r="A3298" s="0">
+        <v>3193</v>
+      </c>
+      <c r="B3298" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3298" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3298" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3298" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће му/јој се дешавати лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3299">
+      <c r="A3299" s="0">
+        <v>3194</v>
+      </c>
+      <c r="B3299" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3299" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3299" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3299" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете не може да се ослободи лоших или чудних мисли из своје главе</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3300">
+      <c r="A3300" s="0">
+        <v>3195</v>
+      </c>
+      <c r="B3300" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3300" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3300" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3300" s="0" t="inlineStr">
+        <is>
+          <t>Када моје дете има неки проблем, срце му/јој брзо куца</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3301">
+      <c r="A3301" s="0">
+        <v>3196</v>
+      </c>
+      <c r="B3301" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3301" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3301" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3301" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете не може да мисли јасно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3302">
+      <c r="A3302" s="0">
+        <v>3197</v>
+      </c>
+      <c r="B3302" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3302" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3302" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3302" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете одједном почне да дрхти или се тресе и без неког разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3303">
+      <c r="A3303" s="0">
+        <v>3198</v>
+      </c>
+      <c r="B3303" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3303" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3303" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3303" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине да ће му/јој се десити нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3304">
+      <c r="A3304" s="0">
+        <v>3199</v>
+      </c>
+      <c r="B3304" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3304" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3304" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3304" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, моје дете осећа да дрхти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3305">
+      <c r="A3305" s="0">
+        <v>3200</v>
+      </c>
+      <c r="B3305" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3305" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3305" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3305" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се осећа безвредно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3306">
+      <c r="A3306" s="0">
+        <v>3201</v>
+      </c>
+      <c r="B3306" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3306" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3306" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3306" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине да ће правити грешке</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3307">
+      <c r="A3307" s="0">
+        <v>3202</v>
+      </c>
+      <c r="B3307" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3307" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3307" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3307" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да мисли о одређеним мислима (као бројеви или речи) да би спечио да се деси нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3308">
+      <c r="A3308" s="0">
+        <v>3203</v>
+      </c>
+      <c r="B3308" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3308" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3308" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3308" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине шта други људи мисле о њему/њој</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3309">
+      <c r="A3309" s="0">
+        <v>3204</v>
+      </c>
+      <c r="B3309" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3309" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3309" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3309" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да буде на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3310">
+      <c r="A3310" s="0">
+        <v>3205</v>
+      </c>
+      <c r="B3310" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3310" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3310" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3310" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се одједном осећам јако уплашено без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3311">
+      <c r="A3311" s="0">
+        <v>3206</v>
+      </c>
+      <c r="B3311" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3311" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3311" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3311" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине шта ће се десити</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3312">
+      <c r="A3312" s="0">
+        <v>3207</v>
+      </c>
+      <c r="B3312" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3312" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3312" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3312" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету се одједном заврти у глави када за то нема разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3313">
+      <c r="A3313" s="0">
+        <v>3208</v>
+      </c>
+      <c r="B3313" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3313" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3313" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3313" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете размишља о смрти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3314">
+      <c r="A3314" s="0">
+        <v>3209</v>
+      </c>
+      <c r="B3314" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3314" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3314" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3314" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се уплаши када треба да прича пред целим разредом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3315">
+      <c r="A3315" s="0">
+        <v>3210</v>
+      </c>
+      <c r="B3315" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3315" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3315" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3315" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету изненада почне срце пребрзо да куца без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3316">
+      <c r="A3316" s="0">
+        <v>3211</v>
+      </c>
+      <c r="B3316" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3316" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3316" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3316" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете изгледа као да не жели да се покреће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3317">
+      <c r="A3317" s="0">
+        <v>3212</v>
+      </c>
+      <c r="B3317" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3317" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3317" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3317" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће изненада имати осећај страха, иако нема чега да се плашим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3318">
+      <c r="A3318" s="0">
+        <v>3213</v>
+      </c>
+      <c r="B3318" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3318" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3318" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3318" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да ради неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3319">
+      <c r="A3319" s="0">
+        <v>3214</v>
+      </c>
+      <c r="B3319" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3319" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3319" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3319" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да ће испасти будала пред другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3320">
+      <c r="A3320" s="0">
+        <v>3215</v>
+      </c>
+      <c r="B3320" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3320" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3320" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3320" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да ради неке ствари на одређени начин да би спречио/ла да се десе лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3321">
+      <c r="A3321" s="0">
+        <v>3216</v>
+      </c>
+      <c r="B3321" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3321" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3321" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3321" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када иде у кревет ноћу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3322">
+      <c r="A3322" s="0">
+        <v>3217</v>
+      </c>
+      <c r="B3322" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3322" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3322" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3322" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете би било уплашено када би морало да преспава ван куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3323">
+      <c r="A3323" s="0">
+        <v>3218</v>
+      </c>
+      <c r="B3323" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3323" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3323" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3323" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете осећа немир</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3324">
+      <c r="A3324" s="0">
+        <v>3219</v>
+      </c>
+      <c r="B3324" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3324" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3324" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3324" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về mọi thứ</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3325">
+      <c r="A3325" s="0">
+        <v>3220</v>
+      </c>
+      <c r="B3325" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3325" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3325" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3325" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy buồn bã hoặc trống rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3326">
+      <c r="A3326" s="0">
+        <v>3221</v>
+      </c>
+      <c r="B3326" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3326" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3326" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3326" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp một vấn đề, em có cảm giác khó chịu trong dạ dày của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3327">
+      <c r="A3327" s="0">
+        <v>3222</v>
+      </c>
+      <c r="B3327" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3327" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3327" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3327" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng khi nghĩ rằng mình đã làm điều gì đó không tốt</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3328">
+      <c r="A3328" s="0">
+        <v>3223</v>
+      </c>
+      <c r="B3328" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3328" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3328" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3328" s="0" t="inlineStr">
+        <is>
+          <t>Em sẽ cảm thấy sợ khi phải ở nhà một mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3329">
+      <c r="A3329" s="0">
+        <v>3224</v>
+      </c>
+      <c r="B3329" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3329" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3329" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3329" s="0" t="inlineStr">
+        <is>
+          <t>Không còn điều gì vui vẻ nữa</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3330">
+      <c r="A3330" s="0">
+        <v>3225</v>
+      </c>
+      <c r="B3330" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3330" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3330" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3330" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi khi phải làm bài kiểm tra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3331">
+      <c r="A3331" s="0">
+        <v>3226</v>
+      </c>
+      <c r="B3331" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3331" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3331" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3331" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy lo lắng khi nghĩ rằng có ai đó đang tức giận với em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3332">
+      <c r="A3332" s="0">
+        <v>3227</v>
+      </c>
+      <c r="B3332" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3332" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3332" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3332" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc phải xa bố mẹ của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3333">
+      <c r="A3333" s="0">
+        <v>3228</v>
+      </c>
+      <c r="B3333" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3333" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3333" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3333" s="0" t="inlineStr">
+        <is>
+          <t>Em bị làm phiền bởi những suy nghĩ hoặc hình ảnh xấu hoặc ngớ ngẩn trong tâm trí của em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3334">
+      <c r="A3334" s="0">
+        <v>3229</v>
+      </c>
+      <c r="B3334" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3334" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3334" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3334" s="0" t="inlineStr">
+        <is>
+          <t>Em bị khó ngủ</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3335">
+      <c r="A3335" s="0">
+        <v>3230</v>
+      </c>
+      <c r="B3335" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3335" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3335" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3335" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng rằng em sẽ làm bài tập ở trường rất kém</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3336">
+      <c r="A3336" s="0">
+        <v>3231</v>
+      </c>
+      <c r="B3336" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3336" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3336" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3336" s="0" t="inlineStr">
+        <is>
+          <t>Em lo rằng điều gì đó khủng khiếp sẽ xảy ra với người thân trong gia đình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3337">
+      <c r="A3337" s="0">
+        <v>3232</v>
+      </c>
+      <c r="B3337" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3337" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3337" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3337" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên cảm thấy như thể em bị khó thở mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3338">
+      <c r="A3338" s="0">
+        <v>3233</v>
+      </c>
+      <c r="B3338" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3338" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3338" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3338" s="0" t="inlineStr">
+        <is>
+          <t>Em có vấn đề với cảm giác thèm ăn của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3339">
+      <c r="A3339" s="0">
+        <v>3234</v>
+      </c>
+      <c r="B3339" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3339" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3339" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3339" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải kiểm tra xem em đã làm đúng chưa (như tắt công tắc chưa hoặc đã khóa cửa chưa)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3340">
+      <c r="A3340" s="0">
+        <v>3235</v>
+      </c>
+      <c r="B3340" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3340" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3340" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3340" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi nếu phải ngủ một mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3341">
+      <c r="A3341" s="0">
+        <v>3236</v>
+      </c>
+      <c r="B3341" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3341" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3341" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3341" s="0" t="inlineStr">
+        <is>
+          <t>Em gặp khó khăn khi đến trường vào buổi sáng vì em cảm thấy lo lắng hoặc sợ hãi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3342">
+      <c r="A3342" s="0">
+        <v>3237</v>
+      </c>
+      <c r="B3342" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3342" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3342" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3342" s="0" t="inlineStr">
+        <is>
+          <t>Em không còn năng lượng cho mọi việc</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3343">
+      <c r="A3343" s="0">
+        <v>3238</v>
+      </c>
+      <c r="B3343" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3343" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3343" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3343" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng mình có thể trông thật ngớ ngẩn</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3344">
+      <c r="A3344" s="0">
+        <v>3239</v>
+      </c>
+      <c r="B3344" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3344" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3344" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3344" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy rất mệt mỏi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3345">
+      <c r="A3345" s="0">
+        <v>3240</v>
+      </c>
+      <c r="B3345" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3345" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3345" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3345" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng vì những điều tồi tệ có thể xảy ra với em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3346">
+      <c r="A3346" s="0">
+        <v>3241</v>
+      </c>
+      <c r="B3346" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3346" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3346" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3346" s="0" t="inlineStr">
+        <is>
+          <t>Em dường như không thể loại bỏ những suy nghĩ xấu hay ngớ ngẩn ra khỏi đầu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3347">
+      <c r="A3347" s="0">
+        <v>3242</v>
+      </c>
+      <c r="B3347" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3347" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3347" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3347" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp vấn đề, tim em đập rất nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3348">
+      <c r="A3348" s="0">
+        <v>3243</v>
+      </c>
+      <c r="B3348" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3348" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3348" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3348" s="0" t="inlineStr">
+        <is>
+          <t>Em không thể suy nghĩ rõ ràng thông suốt</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3349">
+      <c r="A3349" s="0">
+        <v>3244</v>
+      </c>
+      <c r="B3349" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3349" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3349" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3349" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên run rẩy hoặc run lên mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3350">
+      <c r="A3350" s="0">
+        <v>3245</v>
+      </c>
+      <c r="B3350" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3350" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3350" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3350" s="0" t="inlineStr">
+        <is>
+          <t>Em lo rằng chuyện gì đó tồi tệ sẽ xảy ra với mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3351">
+      <c r="A3351" s="0">
+        <v>3246</v>
+      </c>
+      <c r="B3351" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3351" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3351" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3351" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp vấn đề, em cảm thấy run rẩy</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3352">
+      <c r="A3352" s="0">
+        <v>3247</v>
+      </c>
+      <c r="B3352" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3352" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3352" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3352" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy mình vô dụng</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3353">
+      <c r="A3353" s="0">
+        <v>3248</v>
+      </c>
+      <c r="B3353" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3353" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3353" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3353" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc mình sẽ mắc sai lầm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3354">
+      <c r="A3354" s="0">
+        <v>3249</v>
+      </c>
+      <c r="B3354" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3354" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3354" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3354" s="0" t="inlineStr">
+        <is>
+          <t>Em phải nghĩ đến những điều đặc biệt (như con số hoặc từ ngữ nào đó) để ngăn những điều tồi tệ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3355">
+      <c r="A3355" s="0">
+        <v>3250</v>
+      </c>
+      <c r="B3355" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3355" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3355" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3355" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc người khác nghĩ gì về mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3356">
+      <c r="A3356" s="0">
+        <v>3251</v>
+      </c>
+      <c r="B3356" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3356" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3356" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3356" s="0" t="inlineStr">
+        <is>
+          <t>Em sợ hãi khi ở nơi đông người (như trung tâm thương mại, rạp chiếu phim, xe buýt, sân chơi đông đúc)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3357">
+      <c r="A3357" s="0">
+        <v>3252</v>
+      </c>
+      <c r="B3357" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3357" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3357" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3357" s="0" t="inlineStr">
+        <is>
+          <t>Đột nhiên em cảm thấy thực sự sợ hãi mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3358">
+      <c r="A3358" s="0">
+        <v>3253</v>
+      </c>
+      <c r="B3358" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3358" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3358" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3358" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về những gì sẽ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3359">
+      <c r="A3359" s="0">
+        <v>3254</v>
+      </c>
+      <c r="B3359" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3359" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3359" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3359" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên cảm thấy chóng mặt hoặc muốn ngất xỉu mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3360">
+      <c r="A3360" s="0">
+        <v>3255</v>
+      </c>
+      <c r="B3360" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3360" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3360" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3360" s="0" t="inlineStr">
+        <is>
+          <t>Em nghĩ về cái chết</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3361">
+      <c r="A3361" s="0">
+        <v>3256</v>
+      </c>
+      <c r="B3361" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3361" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3361" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3361" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ nếu em phải nói trước lớp</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3362">
+      <c r="A3362" s="0">
+        <v>3257</v>
+      </c>
+      <c r="B3362" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3362" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3362" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3362" s="0" t="inlineStr">
+        <is>
+          <t>Tim em đột nhiên đập quá nhanh mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3363">
+      <c r="A3363" s="0">
+        <v>3258</v>
+      </c>
+      <c r="B3363" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3363" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3363" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3363" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy như thể em không muốn cử động</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3364">
+      <c r="A3364" s="0">
+        <v>3259</v>
+      </c>
+      <c r="B3364" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3364" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3364" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3364" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng rằng mình sẽ đột nhiên cảm thấy sợ hãi dù không có gì đáng sợ cả</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3365">
+      <c r="A3365" s="0">
+        <v>3260</v>
+      </c>
+      <c r="B3365" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3365" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3365" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3365" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải làm một số việc lặp đi lặp lại (như rửa tay, dọn dẹp hoặc sắp xếp mọi thứ theo thứ tự nhất định)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3366">
+      <c r="A3366" s="0">
+        <v>3261</v>
+      </c>
+      <c r="B3366" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3366" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3366" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3366" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy lo sợ rằng mình sẽ làm điều ngu ngốc trước mặt người khác</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3367">
+      <c r="A3367" s="0">
+        <v>3262</v>
+      </c>
+      <c r="B3367" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3367" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3367" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3367" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải làm một số việc theo đúng cách để tránh những chuyện tồi tệ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3368">
+      <c r="A3368" s="0">
+        <v>3263</v>
+      </c>
+      <c r="B3368" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3368" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3368" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3368" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng khi đi ngủ vào ban đêm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3369">
+      <c r="A3369" s="0">
+        <v>3264</v>
+      </c>
+      <c r="B3369" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3369" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3369" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3369" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi nếu em phải xa nhà qua đêm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3370">
+      <c r="A3370" s="0">
         <v>3265</v>
       </c>
-      <c r="B3182" s="0">
+      <c r="B3370" s="0">
         <v>39</v>
       </c>
-      <c r="C3182" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3182" s="0">
+      <c r="C3370" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3370" s="0">
         <v>11</v>
       </c>
-      <c r="E3182" s="0" t="inlineStr">
+      <c r="E3370" s="0" t="inlineStr">
         <is>
           <t>Em cảm thấy bồn chồn</t>
         </is>

--- a/rcads/data/xls/21_ItemStems.xlsx
+++ b/rcads/data/xls/21_ItemStems.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_21_ItemStems"/>
   </sheets>
   <definedNames>
-    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3370</definedName>
+    <definedName name="_21_ItemStems">'_21_ItemStems'!$A$1:$E$3530</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3370"/>
+  <dimension ref="A1:E3530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -62095,2545 +62095,5585 @@
     </row>
     <row outlineLevel="0" r="3237">
       <c r="A3237" s="0">
-        <v>3132</v>
+        <v>3501</v>
       </c>
       <c r="B3237" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3237" s="0">
         <v>1</v>
       </c>
       <c r="D3237" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3237" s="0" t="inlineStr">
         <is>
-          <t>Бринем се када мислим да је неко љут на мене</t>
+          <t>Ndimadandaula za zinthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3238">
       <c r="A3238" s="0">
-        <v>3133</v>
+        <v>3502</v>
       </c>
       <c r="B3238" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3238" s="0">
         <v>1</v>
       </c>
       <c r="D3238" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3238" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да будем далеко од својих родитеља</t>
+          <t>Ndimamva kukhumudwa kapena kupelewera.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3239">
       <c r="A3239" s="0">
-        <v>3134</v>
+        <v>3503</v>
       </c>
       <c r="B3239" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3239" s="0">
         <v>1</v>
       </c>
       <c r="D3239" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3239" s="0" t="inlineStr">
         <is>
-          <t>Узнемиравају ме лоше или чудне мисли и слике у мојој глави</t>
+          <t>Ndikakhala ndi vuto,ndimamva zachilendo mmimba mwanga</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3240">
       <c r="A3240" s="0">
-        <v>3135</v>
+        <v>3504</v>
       </c>
       <c r="B3240" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3240" s="0">
         <v>1</v>
       </c>
       <c r="D3240" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3240" s="0" t="inlineStr">
         <is>
-          <t>Имам проблема са спавањем</t>
+          <t>Ndimadangdaula ndikaganiza kuti sinachite bwino pa chinachake</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3241">
       <c r="A3241" s="0">
-        <v>3136</v>
+        <v>3505</v>
       </c>
       <c r="B3241" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3241" s="0">
         <v>1</v>
       </c>
       <c r="D3241" s="0">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E3241" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ћу урадити лоше задатке на часу</t>
+          <t>Nditha kuchita mantha kukhala ndekha pakhomo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3242">
       <c r="A3242" s="0">
-        <v>3137</v>
+        <v>3506</v>
       </c>
       <c r="B3242" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3242" s="0">
         <v>1</v>
       </c>
       <c r="D3242" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E3242" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ће се десити нешто лоше некоме у мојој породици</t>
+          <t>Palibe chimwe chimndisangalatsa masiku ano</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3243">
       <c r="A3243" s="0">
-        <v>3138</v>
+        <v>3507</v>
       </c>
       <c r="B3243" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3243" s="0">
         <v>1</v>
       </c>
       <c r="D3243" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3243" s="0" t="inlineStr">
         <is>
-          <t>Одједном осећам као да не могу да дишем без икаквог разлога</t>
+          <t>Ndimachita mantha ndikafuna kulemba mayeso</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3244">
       <c r="A3244" s="0">
-        <v>3139</v>
+        <v>3508</v>
       </c>
       <c r="B3244" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3244" s="0">
         <v>1</v>
       </c>
       <c r="D3244" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3244" s="0" t="inlineStr">
         <is>
-          <t>Имам пробелема са апетитом</t>
+          <t>Ndimadandaula ndikaganiza kuti munthu wina wandikwiyira</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3245">
       <c r="A3245" s="0">
-        <v>3140</v>
+        <v>3509</v>
       </c>
       <c r="B3245" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3245" s="0">
         <v>1</v>
       </c>
       <c r="D3245" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3245" s="0" t="inlineStr">
         <is>
-          <t>Морам стално да проверавам да ли сам све урадио/ла како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+          <t>Ndimadandaula ndikakhala kutali ndi makolo anga</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3246">
       <c r="A3246" s="0">
-        <v>3141</v>
+        <v>3510</v>
       </c>
       <c r="B3246" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3246" s="0">
         <v>1</v>
       </c>
       <c r="D3246" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3246" s="0" t="inlineStr">
         <is>
-          <t>Плашим се ако морам да спавам сам/а</t>
+          <t>Ndimavutika ndi Maganizo kapena zithunzithunzi zoyipa kapena zopanda pake mmaganizo mwanga</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3247">
       <c r="A3247" s="0">
-        <v>3142</v>
+        <v>3511</v>
       </c>
       <c r="B3247" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3247" s="0">
         <v>1</v>
       </c>
       <c r="D3247" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E3247" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да идем у школу јер се осећам нервозно или уплашено</t>
+          <t>Ndimavutika kugona</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3248">
       <c r="A3248" s="0">
-        <v>3143</v>
+        <v>3512</v>
       </c>
       <c r="B3248" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3248" s="0">
         <v>1</v>
       </c>
       <c r="D3248" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3248" s="0" t="inlineStr">
         <is>
-          <t>Немам енергије да радим ствари</t>
+          <t>Ndimadandaula kuti sindichita bwino ku sukulu.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3249">
       <c r="A3249" s="0">
-        <v>3144</v>
+        <v>3513</v>
       </c>
       <c r="B3249" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3249" s="0">
         <v>1</v>
       </c>
       <c r="D3249" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3249" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да бих могао/ла да испаднем смешан/а другима</t>
+          <t>Ndimadandaula kuti chinachake choyipa chichitikira wa kiubanja kwathu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3250">
       <c r="A3250" s="0">
-        <v>3145</v>
+        <v>3514</v>
       </c>
       <c r="B3250" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3250" s="0">
         <v>1</v>
       </c>
       <c r="D3250" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3250" s="0" t="inlineStr">
         <is>
-          <t>Много сам уморан/а</t>
+          <t>Pena ndimabanika popanda chifukwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3251">
       <c r="A3251" s="0">
-        <v>3146</v>
+        <v>3515</v>
       </c>
       <c r="B3251" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3251" s="0">
         <v>1</v>
       </c>
       <c r="D3251" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3251" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ће ми се дешавати лоше ствари</t>
+          <t>Ndili ndi vuto la chilakolako cha chakudya</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3252">
       <c r="A3252" s="0">
-        <v>3147</v>
+        <v>3516</v>
       </c>
       <c r="B3252" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3252" s="0">
         <v>1</v>
       </c>
       <c r="D3252" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3252" s="0" t="inlineStr">
         <is>
-          <t>Не могу да се ослободим лоших или чудних мисли из главе</t>
+          <t>Ndimabwereza bwereza kuona ngati ndapanga zinthu molondola(ngati magetsi ndazimitsidwa kapena chitseko chatsekedwa )</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3253">
       <c r="A3253" s="0">
-        <v>3148</v>
+        <v>3517</v>
       </c>
       <c r="B3253" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3253" s="0">
         <v>1</v>
       </c>
       <c r="D3253" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3253" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, срце ми брзо куца</t>
+          <t>Ndimaopa ndikakhala ndigona ndekha</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3254">
       <c r="A3254" s="0">
-        <v>3149</v>
+        <v>3518</v>
       </c>
       <c r="B3254" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3254" s="0">
         <v>1</v>
       </c>
       <c r="D3254" s="0">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3254" s="0" t="inlineStr">
         <is>
-          <t>Не могу да мислим јасно</t>
+          <t>Ndimavutika kupita ku sukulu mmawa chifukwa ndimaopa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3255">
       <c r="A3255" s="0">
-        <v>3150</v>
+        <v>3519</v>
       </c>
       <c r="B3255" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3255" s="0">
         <v>1</v>
       </c>
       <c r="D3255" s="0">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E3255" s="0" t="inlineStr">
         <is>
-          <t>Одједном почнем да дрхтим или се тресем без икаквог разлога</t>
+          <t>Ndiibe mphamvu yopanga zinthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3256">
       <c r="A3256" s="0">
-        <v>3151</v>
+        <v>3520</v>
       </c>
       <c r="B3256" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3256" s="0">
         <v>1</v>
       </c>
       <c r="D3256" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3256" s="0" t="inlineStr">
         <is>
-          <t>Бринем да ће ми се десити нешто лоше</t>
+          <t>Ndimadandaula kuti ndioneka opusa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3257">
       <c r="A3257" s="0">
-        <v>3152</v>
+        <v>3521</v>
       </c>
       <c r="B3257" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3257" s="0">
         <v>1</v>
       </c>
       <c r="D3257" s="0">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3257" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, осећам да дрхтим</t>
+          <t>Ndimatopa kwamnbiri</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3258">
       <c r="A3258" s="0">
-        <v>3153</v>
+        <v>3522</v>
       </c>
       <c r="B3258" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3258" s="0">
         <v>1</v>
       </c>
       <c r="D3258" s="0">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E3258" s="0" t="inlineStr">
         <is>
-          <t>Осећам се безвредно</t>
+          <t>Ndimaopa kuti zinthu zoipa zindichitikira</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3259">
       <c r="A3259" s="0">
-        <v>3154</v>
+        <v>3523</v>
       </c>
       <c r="B3259" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3259" s="0">
         <v>1</v>
       </c>
       <c r="D3259" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3259" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да не правим грешке</t>
+          <t>ndimakanika kuchotsa Maganizo oyipa kapena opanda pake mmaganizo mwanga</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3260">
       <c r="A3260" s="0">
-        <v>3155</v>
+        <v>3524</v>
       </c>
       <c r="B3260" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3260" s="0">
         <v>1</v>
       </c>
       <c r="D3260" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3260" s="0" t="inlineStr">
         <is>
-          <t>Морам да мислим о одређеним мислима (као бројеви или речи) да бих спечио/ла да се деси нешто лоше</t>
+          <t>Ndikakhala ndi vuto mtima wanga umathamanga</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3261">
       <c r="A3261" s="0">
-        <v>3156</v>
+        <v>3525</v>
       </c>
       <c r="B3261" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3261" s="0">
         <v>1</v>
       </c>
       <c r="D3261" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E3261" s="0" t="inlineStr">
         <is>
-          <t>Бринем се шта други људи мисле о мени</t>
+          <t>Sindikuganiza bwino bwino</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3262">
       <c r="A3262" s="0">
-        <v>3157</v>
+        <v>3526</v>
       </c>
       <c r="B3262" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3262" s="0">
         <v>1</v>
       </c>
       <c r="D3262" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3262" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да будем на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+          <t>Ndimangoyamba kunjenjemera popanda chifukwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3263">
       <c r="A3263" s="0">
-        <v>3158</v>
+        <v>3527</v>
       </c>
       <c r="B3263" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3263" s="0">
         <v>1</v>
       </c>
       <c r="D3263" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3263" s="0" t="inlineStr">
         <is>
-          <t>Одједном се осећам јако уплашено без икаквог разлога</t>
+          <t>Ndimaopa kuti china chake choyipa chindichitikira</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3264">
       <c r="A3264" s="0">
-        <v>3159</v>
+        <v>3528</v>
       </c>
       <c r="B3264" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3264" s="0">
         <v>1</v>
       </c>
       <c r="D3264" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3264" s="0" t="inlineStr">
         <is>
-          <t>Бринем се шта ће се десити</t>
+          <t>Ndikakhala ndi vuto ndimanjenjemera/sindikhazikika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3265">
       <c r="A3265" s="0">
-        <v>3160</v>
+        <v>3529</v>
       </c>
       <c r="B3265" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3265" s="0">
         <v>1</v>
       </c>
       <c r="D3265" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3265" s="0" t="inlineStr">
         <is>
-          <t>Одједном ми се заврти у глави без икаквог разлога</t>
+          <t>Ndimadzimva kusafunikira</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3266">
       <c r="A3266" s="0">
-        <v>3161</v>
+        <v>3530</v>
       </c>
       <c r="B3266" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3266" s="0">
         <v>1</v>
       </c>
       <c r="D3266" s="0">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3266" s="0" t="inlineStr">
         <is>
-          <t>Размишљам о смрти</t>
+          <t>Ndimadaula kuti ndilakwitsa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3267">
       <c r="A3267" s="0">
-        <v>3162</v>
+        <v>3531</v>
       </c>
       <c r="B3267" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3267" s="0">
         <v>1</v>
       </c>
       <c r="D3267" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3267" s="0" t="inlineStr">
         <is>
-          <t>Уплашим се када треба да причам пред целим разредом</t>
+          <t>Ndimayika Maganizo anga pa chinachake (monga ma nambala kapena mawu) kuletsa zinthu zoyipa kuti zisachtike</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3268">
       <c r="A3268" s="0">
-        <v>3163</v>
+        <v>3532</v>
       </c>
       <c r="B3268" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3268" s="0">
         <v>1</v>
       </c>
       <c r="D3268" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3268" s="0" t="inlineStr">
         <is>
-          <t>Моје срце одједном почне пребрзо да куца без икаквог разлога</t>
+          <t>Ndimadandaula zomwe anthu akundiganizira.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3269">
       <c r="A3269" s="0">
-        <v>3164</v>
+        <v>3533</v>
       </c>
       <c r="B3269" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3269" s="0">
         <v>1</v>
       </c>
       <c r="D3269" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3269" s="0" t="inlineStr">
         <is>
-          <t>Чини ми се као да не желим да се покрећем</t>
+          <t>Ndimachita mantha kukhala pa malo a gulu (monga malo amalonda, kanema, mu basi, malo osewelela)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3270">
       <c r="A3270" s="0">
-        <v>3165</v>
+        <v>3534</v>
       </c>
       <c r="B3270" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3270" s="0">
         <v>1</v>
       </c>
       <c r="D3270" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E3270" s="0" t="inlineStr">
         <is>
-          <t>Бринем се да ћу изненада имати осећај страха, иако нема чега да се плашим</t>
+          <t>Nimangoyamba kuoanga mantha popanda chifukwa cheni cheni</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3271">
       <c r="A3271" s="0">
-        <v>3166</v>
+        <v>3535</v>
       </c>
       <c r="B3271" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3271" s="0">
         <v>1</v>
       </c>
       <c r="D3271" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3271" s="0" t="inlineStr">
         <is>
-          <t>Морам да радим неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+          <t>Ndimadandaula pa zomwe zingachitike</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3272">
       <c r="A3272" s="0">
-        <v>3167</v>
+        <v>3536</v>
       </c>
       <c r="B3272" s="0">
+        <v>34</v>
+      </c>
+      <c r="C3272" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3272" s="0">
         <v>27</v>
       </c>
-      <c r="C3272" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3272" s="0">
-        <v>2</v>
-      </c>
       <c r="E3272" s="0" t="inlineStr">
         <is>
-          <t>Плашим се да ћу испасти будала пред другима</t>
+          <t>Ndimamva chizungulire apena kukomoka popanda chifukwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3273">
       <c r="A3273" s="0">
-        <v>3168</v>
+        <v>3537</v>
       </c>
       <c r="B3273" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3273" s="0">
         <v>1</v>
       </c>
       <c r="D3273" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3273" s="0" t="inlineStr">
         <is>
-          <t>Морам да радим неке ствари на одређени начин да бих спречио/ла да се десе лоше ствари</t>
+          <t>Ndimganiza za imfa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3274">
       <c r="A3274" s="0">
-        <v>3169</v>
+        <v>3538</v>
       </c>
       <c r="B3274" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3274" s="0">
         <v>1</v>
       </c>
       <c r="D3274" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3274" s="0" t="inlineStr">
         <is>
-          <t>Бринем се када идем у кревет ноћу</t>
+          <t>Ndimachita mantha kulankhula kwa ana anzanga mkalasi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3275">
       <c r="A3275" s="0">
-        <v>3170</v>
+        <v>3539</v>
       </c>
       <c r="B3275" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3275" s="0">
         <v>1</v>
       </c>
       <c r="D3275" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3275" s="0" t="inlineStr">
         <is>
-          <t>Био/ла бих уплашен/а када бих морао/ла да преспавам ван куће</t>
+          <t>Mtima wanga umangoyamba kuthamanga kwambiri popanda chifukwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3276">
       <c r="A3276" s="0">
-        <v>3171</v>
+        <v>3540</v>
       </c>
       <c r="B3276" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3276" s="0">
         <v>1</v>
       </c>
       <c r="D3276" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3276" s="0" t="inlineStr">
         <is>
-          <t>Осећам немир</t>
+          <t>Ndimamva ngati sindikufuna kuyenda</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3277">
       <c r="A3277" s="0">
-        <v>3172</v>
+        <v>3541</v>
       </c>
       <c r="B3277" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3277" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3277" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E3277" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине око разних ствари</t>
+          <t>ndimadandaula kuti ndikhala ndi mantha popanda chowopsa chilichonse</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3278">
       <c r="A3278" s="0">
-        <v>3173</v>
+        <v>3542</v>
       </c>
       <c r="B3278" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3278" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3278" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3278" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се осећа тужно или празно</t>
+          <t>Ndimachita zinthu mobwereza bwereza (monga kusamba manja, kukonza kapena kuyika zinthu mwandondomeko)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3279">
       <c r="A3279" s="0">
-        <v>3174</v>
+        <v>3543</v>
       </c>
       <c r="B3279" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3279" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3279" s="0">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E3279" s="0" t="inlineStr">
         <is>
-          <t>Када моје дете има неки проблем, онда има чудан осећај у стомаку</t>
+          <t>ndimachita mantha kuti ndizichititsa manyazi pa maso pa anthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3280">
       <c r="A3280" s="0">
-        <v>3175</v>
+        <v>3544</v>
       </c>
       <c r="B3280" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3280" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3280" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E3280" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када мисли да је било лоше у нечему</t>
+          <t>Ndimamayenela kuchita zinthu zina moyenela kuti ndiletse zinthu zoyipa kuchitika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3281">
       <c r="A3281" s="0">
-        <v>3176</v>
+        <v>3545</v>
       </c>
       <c r="B3281" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3281" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3281" s="0">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E3281" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да остане само код куће</t>
+          <t>Ndimadandaula ndikamagona usiku</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3282">
       <c r="A3282" s="0">
-        <v>3177</v>
+        <v>3546</v>
       </c>
       <c r="B3282" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3282" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3282" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E3282" s="0" t="inlineStr">
         <is>
-          <t>Мом детету ништа више није забавно</t>
+          <t>Nditha kuchita mantha nditakhala kuti sindinagone kunyumba</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3283">
       <c r="A3283" s="0">
-        <v>3178</v>
+        <v>3547</v>
       </c>
       <c r="B3283" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3283" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3283" s="0">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E3283" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се уплаши када треба да има неки тест</t>
+          <t>Sindimakhazikika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3284">
       <c r="A3284" s="0">
-        <v>3179</v>
+        <v>3548</v>
       </c>
       <c r="B3284" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3284" s="0">
         <v>2</v>
       </c>
       <c r="D3284" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3284" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када мисли да је неко љут на њу/њега</t>
+          <t>Mwana wanga amadandaula za zinthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3285">
       <c r="A3285" s="0">
-        <v>3180</v>
+        <v>3549</v>
       </c>
       <c r="B3285" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3285" s="0">
         <v>2</v>
       </c>
       <c r="D3285" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3285" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да буде одвојено од нас</t>
+          <t>Mwana wanga amamva kukhumudwa kapena kupelewela.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3286">
       <c r="A3286" s="0">
-        <v>3181</v>
+        <v>3550</v>
       </c>
       <c r="B3286" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3286" s="0">
         <v>2</v>
       </c>
       <c r="D3286" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3286" s="0" t="inlineStr">
         <is>
-          <t>Моје дете узнемиравају лоше или чудне мисли и слике у његовој/њеној глави</t>
+          <t>Mwana wanga akakhala ndi vuto amamva zachilendo mmimba mwake</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3287">
       <c r="A3287" s="0">
-        <v>3182</v>
+        <v>3551</v>
       </c>
       <c r="B3287" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3287" s="0">
         <v>2</v>
       </c>
       <c r="D3287" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3287" s="0" t="inlineStr">
         <is>
-          <t>Моје дете има проблема са спавањем</t>
+          <t>Mwana wanga amadandaula akaganizila kuti sanachite bwino pa chinachake</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3288">
       <c r="A3288" s="0">
-        <v>3183</v>
+        <v>3552</v>
       </c>
       <c r="B3288" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3288" s="0">
         <v>2</v>
       </c>
       <c r="D3288" s="0">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="E3288" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће урадити лоше задатке на часу</t>
+          <t>Mwana wanga amachita mantha akakhala ekha khomo</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3289">
       <c r="A3289" s="0">
-        <v>3184</v>
+        <v>3553</v>
       </c>
       <c r="B3289" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3289" s="0">
         <v>2</v>
       </c>
       <c r="D3289" s="0">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E3289" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће се десити нешто лоше некоме у нашој породици</t>
+          <t>Palibe chomwe chikumamusangalatsaso mwana wanga pano.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3290">
       <c r="A3290" s="0">
-        <v>3185</v>
+        <v>3554</v>
       </c>
       <c r="B3290" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3290" s="0">
         <v>2</v>
       </c>
       <c r="D3290" s="0">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3290" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се одједном осећа као да не може да дише без неког разлога</t>
+          <t>Mwana wanga amachita mantha akamalemba mayeso</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3291">
       <c r="A3291" s="0">
-        <v>3186</v>
+        <v>3555</v>
       </c>
       <c r="B3291" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3291" s="0">
         <v>2</v>
       </c>
       <c r="D3291" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3291" s="0" t="inlineStr">
         <is>
-          <t>Моје дете има пробелема са апетитом</t>
+          <t>Mwana wanga amadandaula akamaganizila kuti munthu wina wamukwiyila</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3292">
       <c r="A3292" s="0">
-        <v>3187</v>
+        <v>3556</v>
       </c>
       <c r="B3292" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3292" s="0">
         <v>2</v>
       </c>
       <c r="D3292" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E3292" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора стално да проверава да ли је све урадило како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+          <t>Mwana wanga amadandaula akakhala kutali nane</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3293">
       <c r="A3293" s="0">
-        <v>3188</v>
+        <v>3557</v>
       </c>
       <c r="B3293" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3293" s="0">
         <v>2</v>
       </c>
       <c r="D3293" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3293" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да спава само</t>
+          <t>Mwana wanga amavutisidwa ndi maganizo kapena zithunzithunzi zopanda pake mmaganizo ake</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3294">
       <c r="A3294" s="0">
-        <v>3189</v>
+        <v>3558</v>
       </c>
       <c r="B3294" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3294" s="0">
         <v>2</v>
       </c>
       <c r="D3294" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E3294" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да иде у школу јер се осећа нервозно или уплашено</t>
+          <t>Mwana wanga amavutika kugona.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3295">
       <c r="A3295" s="0">
-        <v>3190</v>
+        <v>3559</v>
       </c>
       <c r="B3295" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3295" s="0">
         <v>2</v>
       </c>
       <c r="D3295" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E3295" s="0" t="inlineStr">
         <is>
-          <t>Моје дете нема енергије да ради ствари</t>
+          <t>Mwana wanga amadandaula pa kusachita bwino ku sukulu.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3296">
       <c r="A3296" s="0">
-        <v>3191</v>
+        <v>3560</v>
       </c>
       <c r="B3296" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3296" s="0">
         <v>2</v>
       </c>
       <c r="D3296" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3296" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да би могало да испадне смешано другима</t>
+          <t>Mwana wanga amadandaula kuti chinthu choopysa chitha kuchitkila anthu apabanja pathu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3297">
       <c r="A3297" s="0">
-        <v>3192</v>
+        <v>3561</v>
       </c>
       <c r="B3297" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3297" s="0">
         <v>2</v>
       </c>
       <c r="D3297" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3297" s="0" t="inlineStr">
         <is>
-          <t>Моје дете је много уморно</t>
+          <t>Mwana wanga amava ngati akubanika popanda chifukwa cheni cheni.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3298">
       <c r="A3298" s="0">
-        <v>3193</v>
+        <v>3562</v>
       </c>
       <c r="B3298" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3298" s="0">
         <v>2</v>
       </c>
       <c r="D3298" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3298" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће му/јој се дешавати лоше ствари</t>
+          <t>Mwana wanga ali ndi vuto ndi chilako lako cha chakudya</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3299">
       <c r="A3299" s="0">
-        <v>3194</v>
+        <v>3563</v>
       </c>
       <c r="B3299" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3299" s="0">
         <v>2</v>
       </c>
       <c r="D3299" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3299" s="0" t="inlineStr">
         <is>
-          <t>Моје дете не може да се ослободи лоших или чудних мисли из своје главе</t>
+          <t>Mwana wanga amabwereza bwereza ngati wapanga zinthu molondola(ngati magetsi wazimitsidwa kapena chitseko chatsekedwa )</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3300">
       <c r="A3300" s="0">
-        <v>3195</v>
+        <v>3564</v>
       </c>
       <c r="B3300" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3300" s="0">
         <v>2</v>
       </c>
       <c r="D3300" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3300" s="0" t="inlineStr">
         <is>
-          <t>Када моје дете има неки проблем, срце му/јој брзо куца</t>
+          <t>Mwana wanga amachita mantha kugona ekha</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3301">
       <c r="A3301" s="0">
-        <v>3196</v>
+        <v>3565</v>
       </c>
       <c r="B3301" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3301" s="0">
         <v>2</v>
       </c>
       <c r="D3301" s="0">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E3301" s="0" t="inlineStr">
         <is>
-          <t>Моје дете не може да мисли јасно</t>
+          <t>Mwana wanga amavutika kupita ku sukulu m’mawa chifukwa amachita mantha</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3302">
       <c r="A3302" s="0">
-        <v>3197</v>
+        <v>3566</v>
       </c>
       <c r="B3302" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3302" s="0">
         <v>2</v>
       </c>
       <c r="D3302" s="0">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E3302" s="0" t="inlineStr">
         <is>
-          <t>Моје дете одједном почне да дрхти или се тресе и без неког разлога</t>
+          <t>Mwana wanga alibe mphavu yopanga zinthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3303">
       <c r="A3303" s="0">
-        <v>3198</v>
+        <v>3567</v>
       </c>
       <c r="B3303" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3303" s="0">
         <v>2</v>
       </c>
       <c r="D3303" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3303" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине да ће му/јој се десити нешто лоше</t>
+          <t>Mwana wanga amadandaula za kuoneka opusa.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3304">
       <c r="A3304" s="0">
-        <v>3199</v>
+        <v>3568</v>
       </c>
       <c r="B3304" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3304" s="0">
         <v>2</v>
       </c>
       <c r="D3304" s="0">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3304" s="0" t="inlineStr">
         <is>
-          <t>Када имам неки проблем, моје дете осећа да дрхти</t>
+          <t>Mwana wanga amakhala otopa kwambiri</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3305">
       <c r="A3305" s="0">
-        <v>3200</v>
+        <v>3569</v>
       </c>
       <c r="B3305" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3305" s="0">
         <v>2</v>
       </c>
       <c r="D3305" s="0">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E3305" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се осећа безвредно</t>
+          <t>Mwana wanga amadandaula kuti zinthu zoyipa zimuchitikila</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3306">
       <c r="A3306" s="0">
-        <v>3201</v>
+        <v>3570</v>
       </c>
       <c r="B3306" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3306" s="0">
         <v>2</v>
       </c>
       <c r="D3306" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3306" s="0" t="inlineStr">
         <is>
-          <t>Моје дете брине да ће правити грешке</t>
+          <t>Mwana wanga amakanika kuchosa maganizo oyipa kapena opanda pake mmaganizo mwake.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3307">
       <c r="A3307" s="0">
-        <v>3202</v>
+        <v>3571</v>
       </c>
       <c r="B3307" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3307" s="0">
         <v>2</v>
       </c>
       <c r="D3307" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3307" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да мисли о одређеним мислима (као бројеви или речи) да би спечио да се деси нешто лоше</t>
+          <t>Mwana wanga akakhala ndi vuto mtima wake umathamanga.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3308">
       <c r="A3308" s="0">
-        <v>3203</v>
+        <v>3572</v>
       </c>
       <c r="B3308" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3308" s="0">
         <v>2</v>
       </c>
       <c r="D3308" s="0">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E3308" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине шта други људи мисле о њему/њој</t>
+          <t>Mwana wanga sakuganiza bwino bwino</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3309">
       <c r="A3309" s="0">
-        <v>3204</v>
+        <v>3573</v>
       </c>
       <c r="B3309" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3309" s="0">
         <v>2</v>
       </c>
       <c r="D3309" s="0">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3309" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да буде на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+          <t>Mwana wanga amangoyamba kunjenjemela opanda chifukwa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3310">
       <c r="A3310" s="0">
-        <v>3205</v>
+        <v>3574</v>
       </c>
       <c r="B3310" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3310" s="0">
         <v>2</v>
       </c>
       <c r="D3310" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3310" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се одједном осећам јако уплашено без икаквог разлога</t>
+          <t>Mwana wanga amadandaula kuti chinachake choyipa chimuchitikila.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3311">
       <c r="A3311" s="0">
-        <v>3206</v>
+        <v>3575</v>
       </c>
       <c r="B3311" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3311" s="0">
         <v>2</v>
       </c>
       <c r="D3311" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3311" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине шта ће се десити</t>
+          <t>Mwana wanga akakhala ndi vuto amanjenjemera/sakhazikika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3312">
       <c r="A3312" s="0">
-        <v>3207</v>
+        <v>3576</v>
       </c>
       <c r="B3312" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3312" s="0">
         <v>2</v>
       </c>
       <c r="D3312" s="0">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E3312" s="0" t="inlineStr">
         <is>
-          <t>Мом детету се одједном заврти у глави када за то нема разлога</t>
+          <t>Mwana wanga amadzimva kusafunikila</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3313">
       <c r="A3313" s="0">
-        <v>3208</v>
+        <v>3577</v>
       </c>
       <c r="B3313" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3313" s="0">
         <v>2</v>
       </c>
       <c r="D3313" s="0">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3313" s="0" t="inlineStr">
         <is>
-          <t>Моје дете размишља о смрти</t>
+          <t>Mwana wanga amadandaula kuti apanga zolakwika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3314">
       <c r="A3314" s="0">
-        <v>3209</v>
+        <v>3578</v>
       </c>
       <c r="B3314" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3314" s="0">
         <v>2</v>
       </c>
       <c r="D3314" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E3314" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се уплаши када треба да прича пред целим разредом</t>
+          <t>Mwana wanga amayika Maganizo pa chinachake (monga ma nambala kapena mawu) kuletsa zinthu zoyipa kuti zisachitike</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3315">
       <c r="A3315" s="0">
-        <v>3210</v>
+        <v>3579</v>
       </c>
       <c r="B3315" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3315" s="0">
         <v>2</v>
       </c>
       <c r="D3315" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3315" s="0" t="inlineStr">
         <is>
-          <t>Мом детету изненада почне срце пребрзо да куца без икаквог разлога</t>
+          <t>Mwana wanga amadandaula pa zomwe anthu akumuganizila.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3316">
       <c r="A3316" s="0">
-        <v>3211</v>
+        <v>3580</v>
       </c>
       <c r="B3316" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3316" s="0">
         <v>2</v>
       </c>
       <c r="D3316" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3316" s="0" t="inlineStr">
         <is>
-          <t>Моје дете изгледа као да не жели да се покреће</t>
+          <t>Mwana wanga amakhala ndi mantha kukhala malo agulu la anthu (monga malo amalonda, kanema, mu basi, malo osewelela)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3317">
       <c r="A3317" s="0">
-        <v>3212</v>
+        <v>3581</v>
       </c>
       <c r="B3317" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3317" s="0">
         <v>2</v>
       </c>
       <c r="D3317" s="0">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E3317" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине да ће изненада имати осећај страха, иако нема чега да се плашим</t>
+          <t>Mwana wanga amangoyamba kupanga mantha popanda chifukwa cheni cheni</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3318">
       <c r="A3318" s="0">
-        <v>3213</v>
+        <v>3582</v>
       </c>
       <c r="B3318" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3318" s="0">
         <v>2</v>
       </c>
       <c r="D3318" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3318" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да ради неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+          <t>Mwana wanga amadandaula pa zomwe zingachitike</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3319">
       <c r="A3319" s="0">
-        <v>3214</v>
+        <v>3583</v>
       </c>
       <c r="B3319" s="0">
+        <v>34</v>
+      </c>
+      <c r="C3319" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3319" s="0">
         <v>27</v>
       </c>
-      <c r="C3319" s="0">
-        <v>2</v>
-      </c>
-      <c r="D3319" s="0">
-        <v>2</v>
-      </c>
       <c r="E3319" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се плаши да ће испасти будала пред другима</t>
+          <t>Mwana wanga amangoyamba kumva chizungulire kapena kukomoka popanda chifukwa.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3320">
       <c r="A3320" s="0">
-        <v>3215</v>
+        <v>3584</v>
       </c>
       <c r="B3320" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3320" s="0">
         <v>2</v>
       </c>
       <c r="D3320" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E3320" s="0" t="inlineStr">
         <is>
-          <t>Моје дете мора да ради неке ствари на одређени начин да би спречио/ла да се десе лоше ствари</t>
+          <t>Mwana wanga amaganiza za imfa</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3321">
       <c r="A3321" s="0">
-        <v>3216</v>
+        <v>3585</v>
       </c>
       <c r="B3321" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3321" s="0">
         <v>2</v>
       </c>
       <c r="D3321" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3321" s="0" t="inlineStr">
         <is>
-          <t>Моје дете се брине када иде у кревет ноћу</t>
+          <t>Mwana wanga amachita mantha akati alankhule kwa ana anzake mkalasi</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3322">
       <c r="A3322" s="0">
-        <v>3217</v>
+        <v>3586</v>
       </c>
       <c r="B3322" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3322" s="0">
         <v>2</v>
       </c>
       <c r="D3322" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3322" s="0" t="inlineStr">
         <is>
-          <t>Моје дете би било уплашено када би морало да преспава ван куће</t>
+          <t>Mwana wanga mtima wake umangoyamba kuthamanga kwambiri popanda chifukwa cheni cheni</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3323">
       <c r="A3323" s="0">
-        <v>3218</v>
+        <v>3587</v>
       </c>
       <c r="B3323" s="0">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C3323" s="0">
         <v>2</v>
       </c>
       <c r="D3323" s="0">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3323" s="0" t="inlineStr">
         <is>
-          <t>Моје дете осећа немир</t>
+          <t>Mwana wanga amamva ngati sakufuna kuyenda</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3324">
       <c r="A3324" s="0">
-        <v>3219</v>
+        <v>3588</v>
       </c>
       <c r="B3324" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3324" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3324" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E3324" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về mọi thứ</t>
+          <t>Mwana wanga amadandaula kuti akhala ndi mantha pamene palibe chowopsya chilichonse</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3325">
       <c r="A3325" s="0">
-        <v>3220</v>
+        <v>3589</v>
       </c>
       <c r="B3325" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3325" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3325" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3325" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy buồn bã hoặc trống rỗng</t>
+          <t>Mwana wanga amachita zinthu mobwereza bwereza (monga kusamba manja, kukonza kapena kuyika zinthu mwandondomeko)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3326">
       <c r="A3326" s="0">
-        <v>3221</v>
+        <v>3590</v>
       </c>
       <c r="B3326" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3326" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3326" s="0">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E3326" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp một vấn đề, em có cảm giác khó chịu trong dạ dày của mình</t>
+          <t>Mwana wanga amachita mantha kuti azichitisa manyazi pamaso pa anthu</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3327">
       <c r="A3327" s="0">
-        <v>3222</v>
+        <v>3591</v>
       </c>
       <c r="B3327" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3327" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3327" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E3327" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng khi nghĩ rằng mình đã làm điều gì đó không tốt</t>
+          <t>Mwana wanga amayenela kuchita zinthu zina moyenela kuti aletse zinthu zoyipa kuchitika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3328">
       <c r="A3328" s="0">
-        <v>3223</v>
+        <v>3592</v>
       </c>
       <c r="B3328" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3328" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3328" s="0">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E3328" s="0" t="inlineStr">
         <is>
-          <t>Em sẽ cảm thấy sợ khi phải ở nhà một mình</t>
+          <t>Mwana wanga amadandaula akakhala malo ake ogona usiku</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3329">
       <c r="A3329" s="0">
-        <v>3224</v>
+        <v>3593</v>
       </c>
       <c r="B3329" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3329" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3329" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E3329" s="0" t="inlineStr">
         <is>
-          <t>Không còn điều gì vui vẻ nữa</t>
+          <t>Mwana wanga atha kuchita mantha atakhala kuti sanagone kunyumba</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3330">
       <c r="A3330" s="0">
-        <v>3225</v>
+        <v>3594</v>
       </c>
       <c r="B3330" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C3330" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3330" s="0">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E3330" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi khi phải làm bài kiểm tra</t>
+          <t>Mwana wanga samakhazikika</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3331">
       <c r="A3331" s="0">
-        <v>3226</v>
+        <v>3595</v>
       </c>
       <c r="B3331" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3331" s="0">
         <v>1</v>
       </c>
       <c r="D3331" s="0">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3331" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy lo lắng khi nghĩ rằng có ai đó đang tức giận với em</t>
+          <t>আমি বিভিন্ন বিষয়ে চিন্তিত থাকি</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3332">
       <c r="A3332" s="0">
-        <v>3227</v>
+        <v>3596</v>
       </c>
       <c r="B3332" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3332" s="0">
         <v>1</v>
       </c>
       <c r="D3332" s="0">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3332" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc phải xa bố mẹ của mình</t>
+          <t>আমি দুঃখ বা শূণ্যতা অনুভব করি</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3333">
       <c r="A3333" s="0">
-        <v>3228</v>
+        <v>3597</v>
       </c>
       <c r="B3333" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3333" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3333" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E3333" s="0" t="inlineStr">
         <is>
-          <t>Em bị làm phiền bởi những suy nghĩ hoặc hình ảnh xấu hoặc ngớ ngẩn trong tâm trí của em</t>
+          <t>When my child has a problem, they get a funny feeling in their stomach</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3334">
       <c r="A3334" s="0">
-        <v>3229</v>
+        <v>3598</v>
       </c>
       <c r="B3334" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3334" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3334" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E3334" s="0" t="inlineStr">
         <is>
-          <t>Em bị khó ngủ</t>
+          <t>My child worries when they think they have done poorly at something</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3335">
       <c r="A3335" s="0">
-        <v>3230</v>
+        <v>3599</v>
       </c>
       <c r="B3335" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3335" s="0">
         <v>1</v>
       </c>
       <c r="D3335" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E3335" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng rằng em sẽ làm bài tập ở trường rất kém</t>
+          <t>ঝামেলায় পড়লে আমার পেটে অস্বস্তি লাগে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3336">
       <c r="A3336" s="0">
-        <v>3231</v>
+        <v>3600</v>
       </c>
       <c r="B3336" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3336" s="0">
         <v>1</v>
       </c>
       <c r="D3336" s="0">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E3336" s="0" t="inlineStr">
         <is>
-          <t>Em lo rằng điều gì đó khủng khiếp sẽ xảy ra với người thân trong gia đình</t>
+          <t>কোন কাজে খারাপ করেছি এমনটা ভাবলে আমি চিন্তায় পড়ে যাই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3337">
       <c r="A3337" s="0">
-        <v>3232</v>
+        <v>3601</v>
       </c>
       <c r="B3337" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3337" s="0">
         <v>1</v>
       </c>
       <c r="D3337" s="0">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E3337" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên cảm thấy như thể em bị khó thở mà không rõ lý do</t>
+          <t>বাসায় একা থাকতে ভয় পাই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3338">
       <c r="A3338" s="0">
-        <v>3233</v>
+        <v>3602</v>
       </c>
       <c r="B3338" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3338" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3338" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3338" s="0" t="inlineStr">
         <is>
-          <t>Em có vấn đề với cảm giác thèm ăn của mình</t>
+          <t>My child worries when they think someone is angry with them</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3339">
       <c r="A3339" s="0">
-        <v>3234</v>
+        <v>3603</v>
       </c>
       <c r="B3339" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3339" s="0">
         <v>1</v>
       </c>
       <c r="D3339" s="0">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E3339" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải kiểm tra xem em đã làm đúng chưa (như tắt công tắc chưa hoặc đã khóa cửa chưa)</t>
+          <t>কিছুই আর আগের মত ততটা আনন্দময় লাগে না</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3340">
       <c r="A3340" s="0">
-        <v>3235</v>
+        <v>3604</v>
       </c>
       <c r="B3340" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3340" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3340" s="0">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3340" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi nếu phải ngủ một mình</t>
+          <t>My child is bothered by bad or silly thoughts or pictures in their mind</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3341">
       <c r="A3341" s="0">
-        <v>3236</v>
+        <v>3605</v>
       </c>
       <c r="B3341" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3341" s="0">
         <v>1</v>
       </c>
       <c r="D3341" s="0">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E3341" s="0" t="inlineStr">
         <is>
-          <t>Em gặp khó khăn khi đến trường vào buổi sáng vì em cảm thấy lo lắng hoặc sợ hãi</t>
+          <t>যখন আমার কোন পরীক্ষা দিতে হয়, তখন আমি ভয় পাই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3342">
       <c r="A3342" s="0">
-        <v>3237</v>
+        <v>3606</v>
       </c>
       <c r="B3342" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3342" s="0">
         <v>1</v>
       </c>
       <c r="D3342" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3342" s="0" t="inlineStr">
         <is>
-          <t>Em không còn năng lượng cho mọi việc</t>
+          <t>কেউ আমার প্রতি রাগ করলে, আমি চিন্তায় পড়ে যাই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3343">
       <c r="A3343" s="0">
-        <v>3238</v>
+        <v>3607</v>
       </c>
       <c r="B3343" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3343" s="0">
         <v>1</v>
       </c>
       <c r="D3343" s="0">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E3343" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng mình có thể trông thật ngớ ngẩn</t>
+          <t>বাবা-মা থেকে দূরে থাকলে আমি চিন্তিত হই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3344">
       <c r="A3344" s="0">
-        <v>3239</v>
+        <v>3608</v>
       </c>
       <c r="B3344" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3344" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3344" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E3344" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy rất mệt mỏi</t>
+          <t>My child suddenly feels as if they can't breathe when there is no reason for this</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3345">
       <c r="A3345" s="0">
-        <v>3240</v>
+        <v>3609</v>
       </c>
       <c r="B3345" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3345" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3345" s="0">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E3345" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng vì những điều tồi tệ có thể xảy ra với em</t>
+          <t>My child has problems with their appetite</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3346">
       <c r="A3346" s="0">
-        <v>3241</v>
+        <v>3610</v>
       </c>
       <c r="B3346" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3346" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3346" s="0">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3346" s="0" t="inlineStr">
         <is>
-          <t>Em dường như không thể loại bỏ những suy nghĩ xấu hay ngớ ngẩn ra khỏi đầu</t>
+          <t>My child has to keep checking that they have done things right (like the switch is off, or the door is locked)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3347">
       <c r="A3347" s="0">
-        <v>3242</v>
+        <v>3611</v>
       </c>
       <c r="B3347" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3347" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3347" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3347" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp vấn đề, tim em đập rất nhanh</t>
+          <t>My child feels scared to sleep on their own</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3348">
       <c r="A3348" s="0">
-        <v>3243</v>
+        <v>3612</v>
       </c>
       <c r="B3348" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3348" s="0">
         <v>1</v>
       </c>
       <c r="D3348" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3348" s="0" t="inlineStr">
         <is>
-          <t>Em không thể suy nghĩ rõ ràng thông suốt</t>
+          <t>আমার মনে খারাপ অথবা অযৌক্তিক চিন্তা অথবা ছবি দ্বারা আমি বিরক্ত হই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3349">
       <c r="A3349" s="0">
-        <v>3244</v>
+        <v>3613</v>
       </c>
       <c r="B3349" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3349" s="0">
         <v>1</v>
       </c>
       <c r="D3349" s="0">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E3349" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên run rẩy hoặc run lên mà không rõ lý do</t>
+          <t>আমার ঘুমের সমস্যা হয়</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3350">
       <c r="A3350" s="0">
-        <v>3245</v>
+        <v>3614</v>
       </c>
       <c r="B3350" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3350" s="0">
         <v>1</v>
       </c>
       <c r="D3350" s="0">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E3350" s="0" t="inlineStr">
         <is>
-          <t>Em lo rằng chuyện gì đó tồi tệ sẽ xảy ra với mình</t>
+          <t>আমার ভয় লাগে যে, আমি লেখাপড়ায় খারাপ করবো</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3351">
       <c r="A3351" s="0">
-        <v>3246</v>
+        <v>3615</v>
       </c>
       <c r="B3351" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3351" s="0">
         <v>1</v>
       </c>
       <c r="D3351" s="0">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E3351" s="0" t="inlineStr">
         <is>
-          <t>Khi em gặp vấn đề, em cảm thấy run rẩy</t>
+          <t>আমার ভয় হয় যে, আমার পরিবারের কারো প্রতি খারাপ কিছু ঘটবে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3352">
       <c r="A3352" s="0">
-        <v>3247</v>
+        <v>3616</v>
       </c>
       <c r="B3352" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3352" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3352" s="0">
         <v>39</v>
       </c>
-      <c r="C3352" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3352" s="0">
-        <v>15</v>
-      </c>
       <c r="E3352" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy mình vô dụng</t>
+          <t>My child worries that bad things will happen to them</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3353">
       <c r="A3353" s="0">
-        <v>3248</v>
+        <v>3617</v>
       </c>
       <c r="B3353" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3353" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3353" s="0">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3353" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc mình sẽ mắc sai lầm</t>
+          <t>My child can't seem to get bad or silly thoughts out of their head.</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3354">
       <c r="A3354" s="0">
-        <v>3249</v>
+        <v>3618</v>
       </c>
       <c r="B3354" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3354" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3354" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3354" s="0" t="inlineStr">
         <is>
-          <t>Em phải nghĩ đến những điều đặc biệt (như con số hoặc từ ngữ nào đó) để ngăn những điều tồi tệ xảy ra</t>
+          <t>When my child has a problem, their heart beats really fast</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3355">
       <c r="A3355" s="0">
-        <v>3250</v>
+        <v>3619</v>
       </c>
       <c r="B3355" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3355" s="0">
         <v>1</v>
       </c>
       <c r="D3355" s="0">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E3355" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về việc người khác nghĩ gì về mình</t>
+          <t>হঠাৎ করে কারন ছাড়াই শ্বাস-প্রশ্বাস নিতে অসুবিধা হচ্ছে বলে আমি অনুভব করি</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3356">
       <c r="A3356" s="0">
-        <v>3251</v>
+        <v>3620</v>
       </c>
       <c r="B3356" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3356" s="0">
         <v>1</v>
       </c>
       <c r="D3356" s="0">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3356" s="0" t="inlineStr">
         <is>
-          <t>Em sợ hãi khi ở nơi đông người (như trung tâm thương mại, rạp chiếu phim, xe buýt, sân chơi đông đúc)</t>
+          <t>আমার খাবার রুচির সমস্যা আছে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3357">
       <c r="A3357" s="0">
-        <v>3252</v>
+        <v>3621</v>
       </c>
       <c r="B3357" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3357" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3357" s="0">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3357" s="0" t="inlineStr">
         <is>
-          <t>Đột nhiên em cảm thấy thực sự sợ hãi mà không rõ lý do</t>
+          <t>My child worries that something bad will happen to them</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3358">
       <c r="A3358" s="0">
-        <v>3253</v>
+        <v>3622</v>
       </c>
       <c r="B3358" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3358" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3358" s="0">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3358" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng về những gì sẽ xảy ra</t>
+          <t>When my child has a problem, they feel shaky</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3359">
       <c r="A3359" s="0">
-        <v>3254</v>
+        <v>3623</v>
       </c>
       <c r="B3359" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3359" s="0">
         <v>1</v>
       </c>
       <c r="D3359" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E3359" s="0" t="inlineStr">
         <is>
-          <t>Em đột nhiên cảm thấy chóng mặt hoặc muốn ngất xỉu mà không rõ lý do</t>
+          <t>আমি কোন কিছু সঠিকভাবে করেছি কিনা তা বারবার দেখতে হয় (যেমন সুইচ বন্ধ বা দরজা বন্ধ করেছি কিনা)</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3360">
       <c r="A3360" s="0">
-        <v>3255</v>
+        <v>3624</v>
       </c>
       <c r="B3360" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3360" s="0">
         <v>1</v>
       </c>
       <c r="D3360" s="0">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E3360" s="0" t="inlineStr">
         <is>
-          <t>Em nghĩ về cái chết</t>
+          <t>একা ঘুমাতে আমার ভয় লাগে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3361">
       <c r="A3361" s="0">
-        <v>3256</v>
+        <v>3625</v>
       </c>
       <c r="B3361" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3361" s="0">
         <v>1</v>
       </c>
       <c r="D3361" s="0">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E3361" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ nếu em phải nói trước lớp</t>
+          <t>সকালে স্কুলে যাওয়ার সময় আমার দুঃশ্চিন্তা ও ভয়ের কারনে সমস্যা হয়</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3362">
       <c r="A3362" s="0">
-        <v>3257</v>
+        <v>3626</v>
       </c>
       <c r="B3362" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3362" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3362" s="0">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E3362" s="0" t="inlineStr">
         <is>
-          <t>Tim em đột nhiên đập quá nhanh mà không rõ lý do</t>
+          <t>My child worries what other people think of them</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3363">
       <c r="A3363" s="0">
-        <v>3258</v>
+        <v>3627</v>
       </c>
       <c r="B3363" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3363" s="0">
         <v>1</v>
       </c>
       <c r="D3363" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3363" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy như thể em không muốn cử động</t>
+          <t>আমি কোন কাজে শক্তি পাই না</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3364">
       <c r="A3364" s="0">
-        <v>3259</v>
+        <v>3628</v>
       </c>
       <c r="B3364" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3364" s="0">
         <v>1</v>
       </c>
       <c r="D3364" s="0">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E3364" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng rằng mình sẽ đột nhiên cảm thấy sợ hãi dù không có gì đáng sợ cả</t>
+          <t>মানুষ আমাকে বোকা ভাবতে পারে বলে আমি ভয় পাই</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3365">
       <c r="A3365" s="0">
-        <v>3260</v>
+        <v>3629</v>
       </c>
       <c r="B3365" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3365" s="0">
         <v>1</v>
       </c>
       <c r="D3365" s="0">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E3365" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải làm một số việc lặp đi lặp lại (như rửa tay, dọn dẹp hoặc sắp xếp mọi thứ theo thứ tự nhất định)</t>
+          <t>আমি অনেক ক্লান্ত</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3366">
       <c r="A3366" s="0">
-        <v>3261</v>
+        <v>3630</v>
       </c>
       <c r="B3366" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3366" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3366" s="0">
         <v>39</v>
       </c>
-      <c r="C3366" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3366" s="0">
-        <v>2</v>
-      </c>
       <c r="E3366" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy lo sợ rằng mình sẽ làm điều ngu ngốc trước mặt người khác</t>
+          <t>আমি ভয় পাই যে, আমার প্রতি খারাপ কিছু ঘটবে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3367">
       <c r="A3367" s="0">
-        <v>3262</v>
+        <v>3631</v>
       </c>
       <c r="B3367" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3367" s="0">
         <v>1</v>
       </c>
       <c r="D3367" s="0">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E3367" s="0" t="inlineStr">
         <is>
-          <t>Em cứ phải làm một số việc theo đúng cách để tránh những chuyện tồi tệ xảy ra</t>
+          <t>আমি আমার মাথা থেকে খারাপ বা তুচ্ছ চিন্তা সরাতে পারি না মনে হচ্ছে</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3368">
       <c r="A3368" s="0">
-        <v>3263</v>
+        <v>3632</v>
       </c>
       <c r="B3368" s="0">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C3368" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3368" s="0">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E3368" s="0" t="inlineStr">
         <is>
-          <t>Em lo lắng khi đi ngủ vào ban đêm</t>
+          <t>My child feels afraid if they have to talk in front of the class</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3369">
       <c r="A3369" s="0">
-        <v>3264</v>
+        <v>3633</v>
       </c>
       <c r="B3369" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C3369" s="0">
         <v>1</v>
       </c>
       <c r="D3369" s="0">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E3369" s="0" t="inlineStr">
         <is>
-          <t>Em cảm thấy sợ hãi nếu em phải xa nhà qua đêm</t>
+          <t>সমস্যায় পড়লে আমার হৃদস্পন্দন বেশ দ্রুত হয়</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="3370">
       <c r="A3370" s="0">
+        <v>3634</v>
+      </c>
+      <c r="B3370" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3370" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3370" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3370" s="0" t="inlineStr">
+        <is>
+          <t>My child feels like they don't want to move</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3371">
+      <c r="A3371" s="0">
+        <v>3635</v>
+      </c>
+      <c r="B3371" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3371" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3371" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3371" s="0" t="inlineStr">
+        <is>
+          <t>My child worries that they will suddenly get a scared feeling when there is nothing to be afraid of</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3372">
+      <c r="A3372" s="0">
+        <v>3636</v>
+      </c>
+      <c r="B3372" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3372" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3372" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3372" s="0" t="inlineStr">
+        <is>
+          <t>আমি সঠিকভাবে চিন্তা করতে পারি না</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3373">
+      <c r="A3373" s="0">
+        <v>3637</v>
+      </c>
+      <c r="B3373" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3373" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3373" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3373" s="0" t="inlineStr">
+        <is>
+          <t>My child feels afraid that they will make a fool of themself in front of people</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3374">
+      <c r="A3374" s="0">
+        <v>3638</v>
+      </c>
+      <c r="B3374" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3374" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3374" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3374" s="0" t="inlineStr">
+        <is>
+          <t>কোন কারণ ছাড়াই আমি হঠাৎ করে কাঁপতে থাকি</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3375">
+      <c r="A3375" s="0">
+        <v>3639</v>
+      </c>
+      <c r="B3375" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3375" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3375" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3375" s="0" t="inlineStr">
+        <is>
+          <t>আমি ভয় পাই যে, আমার সাথে খারাপ কিছু হবে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3376">
+      <c r="A3376" s="0">
+        <v>3640</v>
+      </c>
+      <c r="B3376" s="0">
+        <v>1</v>
+      </c>
+      <c r="C3376" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3376" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3376" s="0" t="inlineStr">
+        <is>
+          <t>My child would feel scared if they had to stay away from home overnight</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3377">
+      <c r="A3377" s="0">
+        <v>3641</v>
+      </c>
+      <c r="B3377" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3377" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3377" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3377" s="0" t="inlineStr">
+        <is>
+          <t>সমস্যায় পড়লে আমি দ্বিধান্বিত হয়ে যাই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3378">
+      <c r="A3378" s="0">
+        <v>3642</v>
+      </c>
+      <c r="B3378" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3378" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3378" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3378" s="0" t="inlineStr">
+        <is>
+          <t>আমার নিজেকে মূল্যহীন মনে হয়</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3379">
+      <c r="A3379" s="0">
+        <v>3643</v>
+      </c>
+      <c r="B3379" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3379" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3379" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3379" s="0" t="inlineStr">
+        <is>
+          <t>আমি দুশ্চিন্তা করি আমার ভুল করা নিয়ে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3380">
+      <c r="A3380" s="0">
+        <v>3644</v>
+      </c>
+      <c r="B3380" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3380" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3380" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3380" s="0" t="inlineStr">
+        <is>
+          <t>খারাপ ঘটনা ঘটা বন্ধ করতে আমাকে নির্দিষ্ট ধরনের চিন্তা করতে হয় (যেমন সংখ্যা বা শব্দ)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3381">
+      <c r="A3381" s="0">
+        <v>3645</v>
+      </c>
+      <c r="B3381" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3381" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3381" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3381" s="0" t="inlineStr">
+        <is>
+          <t>অন্য মানুষ আমার সম্পর্কে কেমন ভাবে তা নিয়ে আমি চিন্তিত থাকি</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3382">
+      <c r="A3382" s="0">
+        <v>3646</v>
+      </c>
+      <c r="B3382" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3382" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3382" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3382" s="0" t="inlineStr">
+        <is>
+          <t>আমি মানুষের ভীড়ে যেতে ভয় পাই (যেমন শপিং সেন্টার, সিনেমা হল, বিপণী বিতান, বাসে, ব্যস্ত খেলার মাঠে)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3383">
+      <c r="A3383" s="0">
+        <v>3647</v>
+      </c>
+      <c r="B3383" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3383" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3383" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3383" s="0" t="inlineStr">
+        <is>
+          <t>হঠাৎ করে আমি কোন কারণ ছাড়াই ভয় পাই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3384">
+      <c r="A3384" s="0">
+        <v>3648</v>
+      </c>
+      <c r="B3384" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3384" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3384" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3384" s="0" t="inlineStr">
+        <is>
+          <t>আমি দুশ্চিন্তা করি কি ঘটতে যাচ্ছে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3385">
+      <c r="A3385" s="0">
+        <v>3649</v>
+      </c>
+      <c r="B3385" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3385" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3385" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3385" s="0" t="inlineStr">
+        <is>
+          <t>কোন কারণ ছাড়াই আমার হঠাৎ মাথা ঘুরায়/নিস্তেজ হয়ে যাই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3386">
+      <c r="A3386" s="0">
+        <v>3650</v>
+      </c>
+      <c r="B3386" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3386" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3386" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3386" s="0" t="inlineStr">
+        <is>
+          <t>আমি মৃত্যু সম্বন্ধে চিন্তা করি</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3387">
+      <c r="A3387" s="0">
+        <v>3651</v>
+      </c>
+      <c r="B3387" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3387" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3387" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3387" s="0" t="inlineStr">
+        <is>
+          <t>আমার শ্রেণীকক্ষে সবার সামনে কথা বলতে ভয় পাই</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3388">
+      <c r="A3388" s="0">
+        <v>3652</v>
+      </c>
+      <c r="B3388" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3388" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3388" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3388" s="0" t="inlineStr">
+        <is>
+          <t>কোন কারণ ছাড়াই আমার হৃদস্পন্দন হঠাৎ বেড়ে যায়</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3389">
+      <c r="A3389" s="0">
+        <v>3653</v>
+      </c>
+      <c r="B3389" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3389" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3389" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3389" s="0" t="inlineStr">
+        <is>
+          <t>আমি অনুভব করি আমি স্থান পরিবর্তন করতে চাই না</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3390">
+      <c r="A3390" s="0">
+        <v>3654</v>
+      </c>
+      <c r="B3390" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3390" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3390" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3390" s="0" t="inlineStr">
+        <is>
+          <t>কোন কারণ ছাড়াই আমি হঠাৎ ভয় পেয়ে যাব বলে আমি চিন্তিত থাকি</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3391">
+      <c r="A3391" s="0">
+        <v>3655</v>
+      </c>
+      <c r="B3391" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3391" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3391" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3391" s="0" t="inlineStr">
+        <is>
+          <t>আমাকে বার বার একই কাজ করতে হয় (যেমন বার বার হাত ধোয়া, পরিষ্কার করা অথবা কোন কিছু নির্দিষ্ট নিয়মে রাখা)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3392">
+      <c r="A3392" s="0">
+        <v>3656</v>
+      </c>
+      <c r="B3392" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3392" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3392" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3392" s="0" t="inlineStr">
+        <is>
+          <t>মানুষের সামনে আমি নিজেকে বোকায় পরিণত করবো বলে আমার ভয় লাগে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3393">
+      <c r="A3393" s="0">
+        <v>3657</v>
+      </c>
+      <c r="B3393" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3393" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3393" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3393" s="0" t="inlineStr">
+        <is>
+          <t>খারাপ কিছু ঘটা বন্ধ করতে আমাকে নির্দিষ্ট নিয়ম মেনে কিছু করতে হয়</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3394">
+      <c r="A3394" s="0">
+        <v>3658</v>
+      </c>
+      <c r="B3394" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3394" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3394" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3394" s="0" t="inlineStr">
+        <is>
+          <t>রাতে ঘুমাতে গেলে আমার ভয় লাগে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3395">
+      <c r="A3395" s="0">
+        <v>3659</v>
+      </c>
+      <c r="B3395" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3395" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3395" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3395" s="0" t="inlineStr">
+        <is>
+          <t>আমি ভয় অনুভব করতাম যদি আমাকে রাতে বাড়ি থেকে দূরে থাকতে হতো</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3396">
+      <c r="A3396" s="0">
+        <v>3660</v>
+      </c>
+      <c r="B3396" s="0">
+        <v>29</v>
+      </c>
+      <c r="C3396" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3396" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3396" s="0" t="inlineStr">
+        <is>
+          <t>আমার অস্থির লাগে</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3397">
+      <c r="A3397" s="0">
+        <v>3132</v>
+      </c>
+      <c r="B3397" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3397" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3397" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3397" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се када мислим да је неко љут на мене</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3398">
+      <c r="A3398" s="0">
+        <v>3133</v>
+      </c>
+      <c r="B3398" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3398" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3398" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3398" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да будем далеко од својих родитеља</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3399">
+      <c r="A3399" s="0">
+        <v>3134</v>
+      </c>
+      <c r="B3399" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3399" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3399" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3399" s="0" t="inlineStr">
+        <is>
+          <t>Узнемиравају ме лоше или чудне мисли и слике у мојој глави</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3400">
+      <c r="A3400" s="0">
+        <v>3135</v>
+      </c>
+      <c r="B3400" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3400" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3400" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3400" s="0" t="inlineStr">
+        <is>
+          <t>Имам проблема са спавањем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3401">
+      <c r="A3401" s="0">
+        <v>3136</v>
+      </c>
+      <c r="B3401" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3401" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3401" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3401" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ћу урадити лоше задатке на часу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3402">
+      <c r="A3402" s="0">
+        <v>3137</v>
+      </c>
+      <c r="B3402" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3402" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3402" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3402" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ће се десити нешто лоше некоме у мојој породици</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3403">
+      <c r="A3403" s="0">
+        <v>3138</v>
+      </c>
+      <c r="B3403" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3403" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3403" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3403" s="0" t="inlineStr">
+        <is>
+          <t>Одједном осећам као да не могу да дишем без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3404">
+      <c r="A3404" s="0">
+        <v>3139</v>
+      </c>
+      <c r="B3404" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3404" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3404" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3404" s="0" t="inlineStr">
+        <is>
+          <t>Имам пробелема са апетитом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3405">
+      <c r="A3405" s="0">
+        <v>3140</v>
+      </c>
+      <c r="B3405" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3405" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3405" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3405" s="0" t="inlineStr">
+        <is>
+          <t>Морам стално да проверавам да ли сам све урадио/ла како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3406">
+      <c r="A3406" s="0">
+        <v>3141</v>
+      </c>
+      <c r="B3406" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3406" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3406" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3406" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се ако морам да спавам сам/а</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3407">
+      <c r="A3407" s="0">
+        <v>3142</v>
+      </c>
+      <c r="B3407" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3407" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3407" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3407" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да идем у школу јер се осећам нервозно или уплашено</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3408">
+      <c r="A3408" s="0">
+        <v>3143</v>
+      </c>
+      <c r="B3408" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3408" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3408" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3408" s="0" t="inlineStr">
+        <is>
+          <t>Немам енергије да радим ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3409">
+      <c r="A3409" s="0">
+        <v>3144</v>
+      </c>
+      <c r="B3409" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3409" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3409" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3409" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да бих могао/ла да испаднем смешан/а другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3410">
+      <c r="A3410" s="0">
+        <v>3145</v>
+      </c>
+      <c r="B3410" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3410" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3410" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3410" s="0" t="inlineStr">
+        <is>
+          <t>Много сам уморан/а</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3411">
+      <c r="A3411" s="0">
+        <v>3146</v>
+      </c>
+      <c r="B3411" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3411" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3411" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3411" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ће ми се дешавати лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3412">
+      <c r="A3412" s="0">
+        <v>3147</v>
+      </c>
+      <c r="B3412" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3412" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3412" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3412" s="0" t="inlineStr">
+        <is>
+          <t>Не могу да се ослободим лоших или чудних мисли из главе</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3413">
+      <c r="A3413" s="0">
+        <v>3148</v>
+      </c>
+      <c r="B3413" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3413" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3413" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3413" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, срце ми брзо куца</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3414">
+      <c r="A3414" s="0">
+        <v>3149</v>
+      </c>
+      <c r="B3414" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3414" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3414" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3414" s="0" t="inlineStr">
+        <is>
+          <t>Не могу да мислим јасно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3415">
+      <c r="A3415" s="0">
+        <v>3150</v>
+      </c>
+      <c r="B3415" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3415" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3415" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3415" s="0" t="inlineStr">
+        <is>
+          <t>Одједном почнем да дрхтим или се тресем без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3416">
+      <c r="A3416" s="0">
+        <v>3151</v>
+      </c>
+      <c r="B3416" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3416" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3416" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3416" s="0" t="inlineStr">
+        <is>
+          <t>Бринем да ће ми се десити нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3417">
+      <c r="A3417" s="0">
+        <v>3152</v>
+      </c>
+      <c r="B3417" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3417" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3417" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3417" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, осећам да дрхтим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3418">
+      <c r="A3418" s="0">
+        <v>3153</v>
+      </c>
+      <c r="B3418" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3418" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3418" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3418" s="0" t="inlineStr">
+        <is>
+          <t>Осећам се безвредно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3419">
+      <c r="A3419" s="0">
+        <v>3154</v>
+      </c>
+      <c r="B3419" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3419" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3419" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3419" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да не правим грешке</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3420">
+      <c r="A3420" s="0">
+        <v>3155</v>
+      </c>
+      <c r="B3420" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3420" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3420" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3420" s="0" t="inlineStr">
+        <is>
+          <t>Морам да мислим о одређеним мислима (као бројеви или речи) да бих спечио/ла да се деси нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3421">
+      <c r="A3421" s="0">
+        <v>3156</v>
+      </c>
+      <c r="B3421" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3421" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3421" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3421" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се шта други људи мисле о мени</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3422">
+      <c r="A3422" s="0">
+        <v>3157</v>
+      </c>
+      <c r="B3422" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3422" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3422" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3422" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да будем на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3423">
+      <c r="A3423" s="0">
+        <v>3158</v>
+      </c>
+      <c r="B3423" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3423" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3423" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3423" s="0" t="inlineStr">
+        <is>
+          <t>Одједном се осећам јако уплашено без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3424">
+      <c r="A3424" s="0">
+        <v>3159</v>
+      </c>
+      <c r="B3424" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3424" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3424" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3424" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се шта ће се десити</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3425">
+      <c r="A3425" s="0">
+        <v>3160</v>
+      </c>
+      <c r="B3425" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3425" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3425" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3425" s="0" t="inlineStr">
+        <is>
+          <t>Одједном ми се заврти у глави без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3426">
+      <c r="A3426" s="0">
+        <v>3161</v>
+      </c>
+      <c r="B3426" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3426" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3426" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3426" s="0" t="inlineStr">
+        <is>
+          <t>Размишљам о смрти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3427">
+      <c r="A3427" s="0">
+        <v>3162</v>
+      </c>
+      <c r="B3427" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3427" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3427" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3427" s="0" t="inlineStr">
+        <is>
+          <t>Уплашим се када треба да причам пред целим разредом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3428">
+      <c r="A3428" s="0">
+        <v>3163</v>
+      </c>
+      <c r="B3428" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3428" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3428" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3428" s="0" t="inlineStr">
+        <is>
+          <t>Моје срце одједном почне пребрзо да куца без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3429">
+      <c r="A3429" s="0">
+        <v>3164</v>
+      </c>
+      <c r="B3429" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3429" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3429" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3429" s="0" t="inlineStr">
+        <is>
+          <t>Чини ми се као да не желим да се покрећем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3430">
+      <c r="A3430" s="0">
+        <v>3165</v>
+      </c>
+      <c r="B3430" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3430" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3430" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3430" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се да ћу изненада имати осећај страха, иако нема чега да се плашим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3431">
+      <c r="A3431" s="0">
+        <v>3166</v>
+      </c>
+      <c r="B3431" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3431" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3431" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3431" s="0" t="inlineStr">
+        <is>
+          <t>Морам да радим неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3432">
+      <c r="A3432" s="0">
+        <v>3167</v>
+      </c>
+      <c r="B3432" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3432" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3432" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3432" s="0" t="inlineStr">
+        <is>
+          <t>Плашим се да ћу испасти будала пред другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3433">
+      <c r="A3433" s="0">
+        <v>3168</v>
+      </c>
+      <c r="B3433" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3433" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3433" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3433" s="0" t="inlineStr">
+        <is>
+          <t>Морам да радим неке ствари на одређени начин да бих спречио/ла да се десе лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3434">
+      <c r="A3434" s="0">
+        <v>3169</v>
+      </c>
+      <c r="B3434" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3434" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3434" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3434" s="0" t="inlineStr">
+        <is>
+          <t>Бринем се када идем у кревет ноћу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3435">
+      <c r="A3435" s="0">
+        <v>3170</v>
+      </c>
+      <c r="B3435" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3435" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3435" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3435" s="0" t="inlineStr">
+        <is>
+          <t>Био/ла бих уплашен/а када бих морао/ла да преспавам ван куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3436">
+      <c r="A3436" s="0">
+        <v>3171</v>
+      </c>
+      <c r="B3436" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3436" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3436" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3436" s="0" t="inlineStr">
+        <is>
+          <t>Осећам немир</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3437">
+      <c r="A3437" s="0">
+        <v>3172</v>
+      </c>
+      <c r="B3437" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3437" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3437" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3437" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине око разних ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3438">
+      <c r="A3438" s="0">
+        <v>3173</v>
+      </c>
+      <c r="B3438" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3438" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3438" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3438" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се осећа тужно или празно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3439">
+      <c r="A3439" s="0">
+        <v>3174</v>
+      </c>
+      <c r="B3439" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3439" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3439" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3439" s="0" t="inlineStr">
+        <is>
+          <t>Када моје дете има неки проблем, онда има чудан осећај у стомаку</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3440">
+      <c r="A3440" s="0">
+        <v>3175</v>
+      </c>
+      <c r="B3440" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3440" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3440" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3440" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када мисли да је било лоше у нечему</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3441">
+      <c r="A3441" s="0">
+        <v>3176</v>
+      </c>
+      <c r="B3441" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3441" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3441" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3441" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да остане само код куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3442">
+      <c r="A3442" s="0">
+        <v>3177</v>
+      </c>
+      <c r="B3442" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3442" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3442" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3442" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету ништа више није забавно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3443">
+      <c r="A3443" s="0">
+        <v>3178</v>
+      </c>
+      <c r="B3443" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3443" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3443" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3443" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се уплаши када треба да има неки тест</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3444">
+      <c r="A3444" s="0">
+        <v>3179</v>
+      </c>
+      <c r="B3444" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3444" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3444" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3444" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када мисли да је неко љут на њу/њега</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3445">
+      <c r="A3445" s="0">
+        <v>3180</v>
+      </c>
+      <c r="B3445" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3445" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3445" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3445" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да буде одвојено од нас</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3446">
+      <c r="A3446" s="0">
+        <v>3181</v>
+      </c>
+      <c r="B3446" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3446" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3446" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3446" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете узнемиравају лоше или чудне мисли и слике у његовој/њеној глави</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3447">
+      <c r="A3447" s="0">
+        <v>3182</v>
+      </c>
+      <c r="B3447" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3447" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3447" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3447" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете има проблема са спавањем</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3448">
+      <c r="A3448" s="0">
+        <v>3183</v>
+      </c>
+      <c r="B3448" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3448" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3448" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3448" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће урадити лоше задатке на часу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3449">
+      <c r="A3449" s="0">
+        <v>3184</v>
+      </c>
+      <c r="B3449" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3449" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3449" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3449" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће се десити нешто лоше некоме у нашој породици</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3450">
+      <c r="A3450" s="0">
+        <v>3185</v>
+      </c>
+      <c r="B3450" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3450" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3450" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3450" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се одједном осећа као да не може да дише без неког разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3451">
+      <c r="A3451" s="0">
+        <v>3186</v>
+      </c>
+      <c r="B3451" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3451" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3451" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3451" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете има пробелема са апетитом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3452">
+      <c r="A3452" s="0">
+        <v>3187</v>
+      </c>
+      <c r="B3452" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3452" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3452" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3452" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора стално да проверава да ли је све урадило како треба (на пример, да ли је прекидач искључен или да ли су врата закључана)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3453">
+      <c r="A3453" s="0">
+        <v>3188</v>
+      </c>
+      <c r="B3453" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3453" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3453" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3453" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да спава само</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3454">
+      <c r="A3454" s="0">
+        <v>3189</v>
+      </c>
+      <c r="B3454" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3454" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3454" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3454" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да иде у школу јер се осећа нервозно или уплашено</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3455">
+      <c r="A3455" s="0">
+        <v>3190</v>
+      </c>
+      <c r="B3455" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3455" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3455" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3455" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете нема енергије да ради ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3456">
+      <c r="A3456" s="0">
+        <v>3191</v>
+      </c>
+      <c r="B3456" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3456" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3456" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3456" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да би могало да испадне смешано другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3457">
+      <c r="A3457" s="0">
+        <v>3192</v>
+      </c>
+      <c r="B3457" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3457" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3457" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3457" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете је много уморно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3458">
+      <c r="A3458" s="0">
+        <v>3193</v>
+      </c>
+      <c r="B3458" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3458" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3458" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3458" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће му/јој се дешавати лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3459">
+      <c r="A3459" s="0">
+        <v>3194</v>
+      </c>
+      <c r="B3459" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3459" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3459" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3459" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете не може да се ослободи лоших или чудних мисли из своје главе</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3460">
+      <c r="A3460" s="0">
+        <v>3195</v>
+      </c>
+      <c r="B3460" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3460" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3460" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3460" s="0" t="inlineStr">
+        <is>
+          <t>Када моје дете има неки проблем, срце му/јој брзо куца</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3461">
+      <c r="A3461" s="0">
+        <v>3196</v>
+      </c>
+      <c r="B3461" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3461" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3461" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3461" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете не може да мисли јасно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3462">
+      <c r="A3462" s="0">
+        <v>3197</v>
+      </c>
+      <c r="B3462" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3462" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3462" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3462" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете одједном почне да дрхти или се тресе и без неког разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3463">
+      <c r="A3463" s="0">
+        <v>3198</v>
+      </c>
+      <c r="B3463" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3463" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3463" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3463" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине да ће му/јој се десити нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3464">
+      <c r="A3464" s="0">
+        <v>3199</v>
+      </c>
+      <c r="B3464" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3464" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3464" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3464" s="0" t="inlineStr">
+        <is>
+          <t>Када имам неки проблем, моје дете осећа да дрхти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3465">
+      <c r="A3465" s="0">
+        <v>3200</v>
+      </c>
+      <c r="B3465" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3465" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3465" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3465" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се осећа безвредно</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3466">
+      <c r="A3466" s="0">
+        <v>3201</v>
+      </c>
+      <c r="B3466" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3466" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3466" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3466" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете брине да ће правити грешке</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3467">
+      <c r="A3467" s="0">
+        <v>3202</v>
+      </c>
+      <c r="B3467" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3467" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3467" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3467" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да мисли о одређеним мислима (као бројеви или речи) да би спечио да се деси нешто лоше</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3468">
+      <c r="A3468" s="0">
+        <v>3203</v>
+      </c>
+      <c r="B3468" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3468" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3468" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3468" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине шта други људи мисле о њему/њој</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3469">
+      <c r="A3469" s="0">
+        <v>3204</v>
+      </c>
+      <c r="B3469" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3469" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3469" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3469" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да буде на местима где има пуно људи (као тржни центри, биоскопи, аутобуси, пуна игралишта)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3470">
+      <c r="A3470" s="0">
+        <v>3205</v>
+      </c>
+      <c r="B3470" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3470" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3470" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3470" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се одједном осећам јако уплашено без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3471">
+      <c r="A3471" s="0">
+        <v>3206</v>
+      </c>
+      <c r="B3471" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3471" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3471" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3471" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине шта ће се десити</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3472">
+      <c r="A3472" s="0">
+        <v>3207</v>
+      </c>
+      <c r="B3472" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3472" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3472" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3472" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету се одједном заврти у глави када за то нема разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3473">
+      <c r="A3473" s="0">
+        <v>3208</v>
+      </c>
+      <c r="B3473" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3473" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3473" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3473" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете размишља о смрти</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3474">
+      <c r="A3474" s="0">
+        <v>3209</v>
+      </c>
+      <c r="B3474" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3474" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3474" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3474" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се уплаши када треба да прича пред целим разредом</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3475">
+      <c r="A3475" s="0">
+        <v>3210</v>
+      </c>
+      <c r="B3475" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3475" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3475" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3475" s="0" t="inlineStr">
+        <is>
+          <t>Мом детету изненада почне срце пребрзо да куца без икаквог разлога</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3476">
+      <c r="A3476" s="0">
+        <v>3211</v>
+      </c>
+      <c r="B3476" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3476" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3476" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3476" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете изгледа као да не жели да се покреће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3477">
+      <c r="A3477" s="0">
+        <v>3212</v>
+      </c>
+      <c r="B3477" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3477" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3477" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3477" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине да ће изненада имати осећај страха, иако нема чега да се плашим</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3478">
+      <c r="A3478" s="0">
+        <v>3213</v>
+      </c>
+      <c r="B3478" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3478" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3478" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3478" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да ради неке ствари изнова и изнова (као што је прање руку, чишћење или ређање ствари по неко редоследу)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3479">
+      <c r="A3479" s="0">
+        <v>3214</v>
+      </c>
+      <c r="B3479" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3479" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3479" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3479" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се плаши да ће испасти будала пред другима</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3480">
+      <c r="A3480" s="0">
+        <v>3215</v>
+      </c>
+      <c r="B3480" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3480" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3480" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3480" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете мора да ради неке ствари на одређени начин да би спречио/ла да се десе лоше ствари</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3481">
+      <c r="A3481" s="0">
+        <v>3216</v>
+      </c>
+      <c r="B3481" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3481" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3481" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3481" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете се брине када иде у кревет ноћу</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3482">
+      <c r="A3482" s="0">
+        <v>3217</v>
+      </c>
+      <c r="B3482" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3482" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3482" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3482" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете би било уплашено када би морало да преспава ван куће</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3483">
+      <c r="A3483" s="0">
+        <v>3218</v>
+      </c>
+      <c r="B3483" s="0">
+        <v>27</v>
+      </c>
+      <c r="C3483" s="0">
+        <v>2</v>
+      </c>
+      <c r="D3483" s="0">
+        <v>11</v>
+      </c>
+      <c r="E3483" s="0" t="inlineStr">
+        <is>
+          <t>Моје дете осећа немир</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3484">
+      <c r="A3484" s="0">
+        <v>3219</v>
+      </c>
+      <c r="B3484" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3484" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3484" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3484" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về mọi thứ</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3485">
+      <c r="A3485" s="0">
+        <v>3220</v>
+      </c>
+      <c r="B3485" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3485" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3485" s="0">
+        <v>12</v>
+      </c>
+      <c r="E3485" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy buồn bã hoặc trống rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3486">
+      <c r="A3486" s="0">
+        <v>3221</v>
+      </c>
+      <c r="B3486" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3486" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3486" s="0">
+        <v>35</v>
+      </c>
+      <c r="E3486" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp một vấn đề, em có cảm giác khó chịu trong dạ dày của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3487">
+      <c r="A3487" s="0">
+        <v>3222</v>
+      </c>
+      <c r="B3487" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3487" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3487" s="0">
+        <v>45</v>
+      </c>
+      <c r="E3487" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng khi nghĩ rằng mình đã làm điều gì đó không tốt</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3488">
+      <c r="A3488" s="0">
+        <v>3223</v>
+      </c>
+      <c r="B3488" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3488" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3488" s="0">
+        <v>7</v>
+      </c>
+      <c r="E3488" s="0" t="inlineStr">
+        <is>
+          <t>Em sẽ cảm thấy sợ khi phải ở nhà một mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3489">
+      <c r="A3489" s="0">
+        <v>3224</v>
+      </c>
+      <c r="B3489" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3489" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3489" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3489" s="0" t="inlineStr">
+        <is>
+          <t>Không còn điều gì vui vẻ nữa</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3490">
+      <c r="A3490" s="0">
+        <v>3225</v>
+      </c>
+      <c r="B3490" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3490" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3490" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3490" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi khi phải làm bài kiểm tra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3491">
+      <c r="A3491" s="0">
+        <v>3226</v>
+      </c>
+      <c r="B3491" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3491" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3491" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3491" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy lo lắng khi nghĩ rằng có ai đó đang tức giận với em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3492">
+      <c r="A3492" s="0">
+        <v>3227</v>
+      </c>
+      <c r="B3492" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3492" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3492" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3492" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc phải xa bố mẹ của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3493">
+      <c r="A3493" s="0">
+        <v>3228</v>
+      </c>
+      <c r="B3493" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3493" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3493" s="0">
+        <v>4</v>
+      </c>
+      <c r="E3493" s="0" t="inlineStr">
+        <is>
+          <t>Em bị làm phiền bởi những suy nghĩ hoặc hình ảnh xấu hoặc ngớ ngẩn trong tâm trí của em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3494">
+      <c r="A3494" s="0">
+        <v>3229</v>
+      </c>
+      <c r="B3494" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3494" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3494" s="0">
+        <v>21</v>
+      </c>
+      <c r="E3494" s="0" t="inlineStr">
+        <is>
+          <t>Em bị khó ngủ</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3495">
+      <c r="A3495" s="0">
+        <v>3230</v>
+      </c>
+      <c r="B3495" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3495" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3495" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3495" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng rằng em sẽ làm bài tập ở trường rất kém</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3496">
+      <c r="A3496" s="0">
+        <v>3231</v>
+      </c>
+      <c r="B3496" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3496" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3496" s="0">
+        <v>42</v>
+      </c>
+      <c r="E3496" s="0" t="inlineStr">
+        <is>
+          <t>Em lo rằng điều gì đó khủng khiếp sẽ xảy ra với người thân trong gia đình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3497">
+      <c r="A3497" s="0">
+        <v>3232</v>
+      </c>
+      <c r="B3497" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3497" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3497" s="0">
+        <v>29</v>
+      </c>
+      <c r="E3497" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên cảm thấy như thể em bị khó thở mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3498">
+      <c r="A3498" s="0">
+        <v>3233</v>
+      </c>
+      <c r="B3498" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3498" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3498" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3498" s="0" t="inlineStr">
+        <is>
+          <t>Em có vấn đề với cảm giác thèm ăn của mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3499">
+      <c r="A3499" s="0">
+        <v>3234</v>
+      </c>
+      <c r="B3499" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3499" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3499" s="0">
+        <v>23</v>
+      </c>
+      <c r="E3499" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải kiểm tra xem em đã làm đúng chưa (như tắt công tắc chưa hoặc đã khóa cửa chưa)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3500">
+      <c r="A3500" s="0">
+        <v>3235</v>
+      </c>
+      <c r="B3500" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3500" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3500" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3500" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi nếu phải ngủ một mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3501">
+      <c r="A3501" s="0">
+        <v>3236</v>
+      </c>
+      <c r="B3501" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3501" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3501" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3501" s="0" t="inlineStr">
+        <is>
+          <t>Em gặp khó khăn khi đến trường vào buổi sáng vì em cảm thấy lo lắng hoặc sợ hãi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3502">
+      <c r="A3502" s="0">
+        <v>3237</v>
+      </c>
+      <c r="B3502" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3502" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3502" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3502" s="0" t="inlineStr">
+        <is>
+          <t>Em không còn năng lượng cho mọi việc</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3503">
+      <c r="A3503" s="0">
+        <v>3238</v>
+      </c>
+      <c r="B3503" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3503" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3503" s="0">
+        <v>41</v>
+      </c>
+      <c r="E3503" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng mình có thể trông thật ngớ ngẩn</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3504">
+      <c r="A3504" s="0">
+        <v>3239</v>
+      </c>
+      <c r="B3504" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3504" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3504" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3504" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy rất mệt mỏi</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3505">
+      <c r="A3505" s="0">
+        <v>3240</v>
+      </c>
+      <c r="B3505" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3505" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3505" s="0">
+        <v>39</v>
+      </c>
+      <c r="E3505" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng vì những điều tồi tệ có thể xảy ra với em</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3506">
+      <c r="A3506" s="0">
+        <v>3241</v>
+      </c>
+      <c r="B3506" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3506" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3506" s="0">
+        <v>6</v>
+      </c>
+      <c r="E3506" s="0" t="inlineStr">
+        <is>
+          <t>Em dường như không thể loại bỏ những suy nghĩ xấu hay ngớ ngẩn ra khỏi đầu</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3507">
+      <c r="A3507" s="0">
+        <v>3242</v>
+      </c>
+      <c r="B3507" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3507" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3507" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3507" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp vấn đề, tim em đập rất nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3508">
+      <c r="A3508" s="0">
+        <v>3243</v>
+      </c>
+      <c r="B3508" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3508" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3508" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3508" s="0" t="inlineStr">
+        <is>
+          <t>Em không thể suy nghĩ rõ ràng thông suốt</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3509">
+      <c r="A3509" s="0">
+        <v>3244</v>
+      </c>
+      <c r="B3509" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3509" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3509" s="0">
+        <v>30</v>
+      </c>
+      <c r="E3509" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên run rẩy hoặc run lên mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3510">
+      <c r="A3510" s="0">
+        <v>3245</v>
+      </c>
+      <c r="B3510" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3510" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3510" s="0">
+        <v>43</v>
+      </c>
+      <c r="E3510" s="0" t="inlineStr">
+        <is>
+          <t>Em lo rằng chuyện gì đó tồi tệ sẽ xảy ra với mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3511">
+      <c r="A3511" s="0">
+        <v>3246</v>
+      </c>
+      <c r="B3511" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3511" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3511" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3511" s="0" t="inlineStr">
+        <is>
+          <t>Khi em gặp vấn đề, em cảm thấy run rẩy</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3512">
+      <c r="A3512" s="0">
+        <v>3247</v>
+      </c>
+      <c r="B3512" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3512" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3512" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3512" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy mình vô dụng</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3513">
+      <c r="A3513" s="0">
+        <v>3248</v>
+      </c>
+      <c r="B3513" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3513" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3513" s="0">
+        <v>36</v>
+      </c>
+      <c r="E3513" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc mình sẽ mắc sai lầm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3514">
+      <c r="A3514" s="0">
+        <v>3249</v>
+      </c>
+      <c r="B3514" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3514" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3514" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3514" s="0" t="inlineStr">
+        <is>
+          <t>Em phải nghĩ đến những điều đặc biệt (như con số hoặc từ ngữ nào đó) để ngăn những điều tồi tệ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3515">
+      <c r="A3515" s="0">
+        <v>3250</v>
+      </c>
+      <c r="B3515" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3515" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3515" s="0">
+        <v>44</v>
+      </c>
+      <c r="E3515" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về việc người khác nghĩ gì về mình</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3516">
+      <c r="A3516" s="0">
+        <v>3251</v>
+      </c>
+      <c r="B3516" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3516" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3516" s="0">
+        <v>1</v>
+      </c>
+      <c r="E3516" s="0" t="inlineStr">
+        <is>
+          <t>Em sợ hãi khi ở nơi đông người (như trung tâm thương mại, rạp chiếu phim, xe buýt, sân chơi đông đúc)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3517">
+      <c r="A3517" s="0">
+        <v>3252</v>
+      </c>
+      <c r="B3517" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3517" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3517" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3517" s="0" t="inlineStr">
+        <is>
+          <t>Đột nhiên em cảm thấy thực sự sợ hãi mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3518">
+      <c r="A3518" s="0">
+        <v>3253</v>
+      </c>
+      <c r="B3518" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3518" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3518" s="0">
+        <v>38</v>
+      </c>
+      <c r="E3518" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng về những gì sẽ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3519">
+      <c r="A3519" s="0">
+        <v>3254</v>
+      </c>
+      <c r="B3519" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3519" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3519" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3519" s="0" t="inlineStr">
+        <is>
+          <t>Em đột nhiên cảm thấy chóng mặt hoặc muốn ngất xỉu mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3520">
+      <c r="A3520" s="0">
+        <v>3255</v>
+      </c>
+      <c r="B3520" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3520" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3520" s="0">
+        <v>31</v>
+      </c>
+      <c r="E3520" s="0" t="inlineStr">
+        <is>
+          <t>Em nghĩ về cái chết</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3521">
+      <c r="A3521" s="0">
+        <v>3256</v>
+      </c>
+      <c r="B3521" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3521" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3521" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3521" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ nếu em phải nói trước lớp</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3522">
+      <c r="A3522" s="0">
+        <v>3257</v>
+      </c>
+      <c r="B3522" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3522" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3522" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3522" s="0" t="inlineStr">
+        <is>
+          <t>Tim em đột nhiên đập quá nhanh mà không rõ lý do</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3523">
+      <c r="A3523" s="0">
+        <v>3258</v>
+      </c>
+      <c r="B3523" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3523" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3523" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3523" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy như thể em không muốn cử động</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3524">
+      <c r="A3524" s="0">
+        <v>3259</v>
+      </c>
+      <c r="B3524" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3524" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3524" s="0">
+        <v>47</v>
+      </c>
+      <c r="E3524" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng rằng mình sẽ đột nhiên cảm thấy sợ hãi dù không có gì đáng sợ cả</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3525">
+      <c r="A3525" s="0">
+        <v>3260</v>
+      </c>
+      <c r="B3525" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3525" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3525" s="0">
+        <v>19</v>
+      </c>
+      <c r="E3525" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải làm một số việc lặp đi lặp lại (như rửa tay, dọn dẹp hoặc sắp xếp mọi thứ theo thứ tự nhất định)</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3526">
+      <c r="A3526" s="0">
+        <v>3261</v>
+      </c>
+      <c r="B3526" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3526" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3526" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3526" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy lo sợ rằng mình sẽ làm điều ngu ngốc trước mặt người khác</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3527">
+      <c r="A3527" s="0">
+        <v>3262</v>
+      </c>
+      <c r="B3527" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3527" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3527" s="0">
+        <v>18</v>
+      </c>
+      <c r="E3527" s="0" t="inlineStr">
+        <is>
+          <t>Em cứ phải làm một số việc theo đúng cách để tránh những chuyện tồi tệ xảy ra</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3528">
+      <c r="A3528" s="0">
+        <v>3263</v>
+      </c>
+      <c r="B3528" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3528" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3528" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3528" s="0" t="inlineStr">
+        <is>
+          <t>Em lo lắng khi đi ngủ vào ban đêm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3529">
+      <c r="A3529" s="0">
+        <v>3264</v>
+      </c>
+      <c r="B3529" s="0">
+        <v>39</v>
+      </c>
+      <c r="C3529" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3529" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3529" s="0" t="inlineStr">
+        <is>
+          <t>Em cảm thấy sợ hãi nếu em phải xa nhà qua đêm</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3530">
+      <c r="A3530" s="0">
         <v>3265</v>
       </c>
-      <c r="B3370" s="0">
+      <c r="B3530" s="0">
         <v>39</v>
       </c>
-      <c r="C3370" s="0">
-        <v>1</v>
-      </c>
-      <c r="D3370" s="0">
+      <c r="C3530" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3530" s="0">
         <v>11</v>
       </c>
-      <c r="E3370" s="0" t="inlineStr">
+      <c r="E3530" s="0" t="inlineStr">
         <is>
           <t>Em cảm thấy bồn chồn</t>
         </is>
